--- a/docs/data/jp/xlsx/3091.xlsx
+++ b/docs/data/jp/xlsx/3091.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -759,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC190"/>
+  <dimension ref="A1:AC197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4349,11 +4352,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>3130</v>
+        <v>3160</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5590,7 +5593,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5836,576 +5839,641 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>1951.839</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2141</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>2031</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>2334</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>2109</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>2496</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>2395</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>2552</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>2471</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>2666</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>2572</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>2936</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>1951.839</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>2109</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>2471</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>3900.283</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>4385</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>4127</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>4934</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>4555</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>4788</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>4911</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>5327</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>5278</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>5575</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>5661</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>5940</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>3900.283</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>4555</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>5278</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>3446.758</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>3607</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>3683</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>4141</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>4255</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>4219</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>4493</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>4407</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>4544</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>4763</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>4815</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>3446.758</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>4039</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>4407</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>453.524</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>777</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>444</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>794</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>516</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>532</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>692</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>834</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>872</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>1031</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>898</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>1125</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>453.524</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>516</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>872</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.607</v>
+        <v>3446.758</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>1</v>
+        <v>3607</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>1</v>
+        <v>3683</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>2</v>
+        <v>4141</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>3</v>
+        <v>4039</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>2</v>
+        <v>4255</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>3</v>
+        <v>4219</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>3</v>
+        <v>4493</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>4</v>
+        <v>4407</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>2</v>
+        <v>4544</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>4</v>
+        <v>4763</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>5</v>
+        <v>4815</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.607</v>
+        <v>3446.758</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>3</v>
+        <v>4039</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>4</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>1</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>453.524</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>777</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>444</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>794</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>516</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>532</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>692</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>834</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>872</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>1031</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>898</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>1125</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>453.524</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>516</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>872</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>임대료 수익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>9.507</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>9.507</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>6</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>협찬금 수입</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>13.608</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>13.608</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>14</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H87" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" s="22" t="n">
+        <v>3</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V87" s="22" t="n">
+        <v>0.607</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>-0.672</v>
+        <v>0.907</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E88" s="22" t="n">
         <v>2</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I88" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J88" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="K88" s="22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>-0.672</v>
+        <v>0.907</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>임대료 수익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>32.565</v>
+        <v>9.507</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>32.565</v>
+        <v>9.507</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>협찬금 수입</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0.134</v>
+        <v>13.608</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L90" s="22" t="n">
         <v>0</v>
@@ -6417,65 +6485,32 @@
         <v>0</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0.134</v>
+        <v>13.608</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>임대비용</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>5.953</v>
-      </c>
-      <c r="D91" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="F91" s="22" t="n">
-        <v>5</v>
+          <t>투자유가증권 매각이익</t>
+        </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>5.953</v>
+        <v>0</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -6485,843 +6520,817 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>1.994</v>
+        <v>-0.672</v>
       </c>
       <c r="D92" s="22" t="n">
         <v>3</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I92" s="22" t="n">
         <v>2</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>1</v>
       </c>
       <c r="J92" s="22" t="n">
         <v>3</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L92" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>1.994</v>
+        <v>-0.672</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>8.082000000000001</v>
+        <v>32.565</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>8.082000000000001</v>
+        <v>32.565</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>478.008</v>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>793</v>
-      </c>
-      <c r="E94" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>810</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>542</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>553</v>
-      </c>
-      <c r="I94" s="12" t="n">
-        <v>705</v>
-      </c>
-      <c r="J94" s="12" t="n">
-        <v>874</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>893</v>
-      </c>
-      <c r="L94" s="12" t="n">
-        <v>1037</v>
-      </c>
-      <c r="M94" s="12" t="n">
-        <v>904</v>
-      </c>
-      <c r="N94" s="12" t="n">
-        <v>1132</v>
-      </c>
-      <c r="V94" s="12" t="n">
-        <v>478.008</v>
-      </c>
-      <c r="W94" s="12" t="n">
-        <v>542</v>
-      </c>
-      <c r="X94" s="12" t="n">
-        <v>893</v>
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
-        </is>
+          <t>임대비용</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>5.953</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>5.953</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>6</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>3</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손실</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>1.422</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I97" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K97" s="22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L97" s="22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M97" s="22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N97" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V97" s="22" t="n">
-        <v>1.422</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="W97" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X97" s="22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>200.647</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>176</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>249</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>200.647</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>176</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>249</v>
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>478.008</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>793</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>542</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>553</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>705</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>874</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>893</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>1037</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>904</v>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>1132</v>
+      </c>
+      <c r="V98" s="12" t="n">
+        <v>478.008</v>
+      </c>
+      <c r="W98" s="12" t="n">
+        <v>542</v>
+      </c>
+      <c r="X98" s="12" t="n">
+        <v>893</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>7</v>
+      <c r="A99" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G99" s="17">
+        <f>IF(OR(G98="",C98=""),"",IF(C98&lt;=0,"",IFERROR(G98/C98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H99" s="17">
+        <f>IF(OR(H98="",D98=""),"",IF(D98&lt;=0,"",IFERROR(H98/D98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I99" s="17">
+        <f>IF(OR(I98="",E98=""),"",IF(E98&lt;=0,"",IFERROR(I98/E98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J99" s="17">
+        <f>IF(OR(J98="",F98=""),"",IF(F98&lt;=0,"",IFERROR(J98/F98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K99" s="17">
+        <f>IF(OR(K98="",G98=""),"",IF(G98&lt;=0,"",IFERROR(K98/G98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L99" s="17">
+        <f>IF(OR(L98="",H98=""),"",IF(H98&lt;=0,"",IFERROR(L98/H98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M99" s="17">
+        <f>IF(OR(M98="",I98=""),"",IF(I98&lt;=0,"",IFERROR(M98/I98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N99" s="17">
+        <f>IF(OR(N98="",J98=""),"",IF(J98&lt;=0,"",IFERROR(N98/J98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V99" s="17">
+        <f>IF(OR(V98="",U98=""),"",IF(U98&lt;=0,"",IFERROR(V98/U98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W99" s="17">
+        <f>IF(OR(W98="",V98=""),"",IF(V98&lt;=0,"",IFERROR(W98/V98-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X99" s="17">
+        <f>IF(OR(X98="",W98=""),"",IF(W98&lt;=0,"",IFERROR(X98/W98-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>202.068</v>
-      </c>
-      <c r="D100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>185</v>
-      </c>
-      <c r="H100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>0</v>
+          <t>고정자산 매각이익</t>
+        </is>
       </c>
       <c r="J100" s="22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K100" s="22" t="n">
-        <v>250</v>
-      </c>
-      <c r="L100" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M100" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>202.068</v>
-      </c>
-      <c r="W100" s="22" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="X100" s="22" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>276.125</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>793</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>454</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>810</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>358</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>552</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>705</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>860</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>643</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>1035</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>904</v>
-      </c>
-      <c r="N101" s="12" t="n">
-        <v>1131</v>
-      </c>
-      <c r="V101" s="12" t="n">
-        <v>276.125</v>
-      </c>
-      <c r="W101" s="12" t="n">
-        <v>358</v>
-      </c>
-      <c r="X101" s="12" t="n">
-        <v>643</v>
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>고정자산 제각·매각손실</t>
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>50.059</v>
+        <v>1.422</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>351</v>
+        <v>2</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="L102" s="22" t="n">
-        <v>364</v>
+        <v>1</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>285</v>
+        <v>1</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>440</v>
+        <v>1</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>50.059</v>
+        <v>1.422</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>-39.193</v>
-      </c>
-      <c r="D103" s="22" t="n">
-        <v>-33</v>
-      </c>
-      <c r="E103" s="22" t="n">
-        <v>59</v>
+        <v>200.647</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>-67</v>
+        <v>0</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H103" s="22" t="n">
-        <v>-41</v>
-      </c>
-      <c r="I103" s="22" t="n">
-        <v>56</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>-69</v>
+        <v>176</v>
       </c>
       <c r="K103" s="22" t="n">
-        <v>-43</v>
-      </c>
-      <c r="L103" s="22" t="n">
-        <v>-22</v>
-      </c>
-      <c r="M103" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>-67</v>
+        <v>249</v>
       </c>
       <c r="V103" s="22" t="n">
-        <v>-39.193</v>
+        <v>200.647</v>
       </c>
       <c r="W103" s="22" t="n">
-        <v>-13</v>
+        <v>176</v>
       </c>
       <c r="X103" s="22" t="n">
-        <v>-43</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C104" s="22" t="n">
-        <v>10.865</v>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>265</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>179</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>237</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>282</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>93</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>341</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>308</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>372</v>
+        <v>7</v>
       </c>
       <c r="V104" s="22" t="n">
-        <v>10.865</v>
+        <v>0</v>
       </c>
       <c r="W104" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>93</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>265.259</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>527</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>296</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>346</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>373</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>468</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>578</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>550</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>693</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>596</v>
-      </c>
-      <c r="N105" s="12" t="n">
-        <v>760</v>
-      </c>
-      <c r="V105" s="12" t="n">
-        <v>265.259</v>
-      </c>
-      <c r="W105" s="12" t="n">
-        <v>346</v>
-      </c>
-      <c r="X105" s="12" t="n">
-        <v>550</v>
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>202.068</v>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>185</v>
+      </c>
+      <c r="H105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>250</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>202.068</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>185</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C106" s="12" t="n">
-        <v>265.259</v>
+        <v>276.125</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>527</v>
+        <v>793</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>296</v>
+        <v>454</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>546</v>
+        <v>810</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>373</v>
+        <v>552</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>468</v>
+        <v>705</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>578</v>
+        <v>860</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>550</v>
+        <v>643</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>693</v>
+        <v>1035</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>596</v>
+        <v>904</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>760</v>
+        <v>1131</v>
       </c>
       <c r="V106" s="12" t="n">
-        <v>265.259</v>
+        <v>276.125</v>
       </c>
       <c r="W106" s="12" t="n">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="X106" s="12" t="n">
-        <v>550</v>
+        <v>643</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>50.059</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>299</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>332</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>221</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>180</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>351</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>136</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>364</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>285</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>440</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>50.059</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B108" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-      <c r="J108" s="18" t="n"/>
-      <c r="K108" s="18" t="n"/>
-      <c r="L108" s="18" t="n"/>
-      <c r="M108" s="18" t="n"/>
-      <c r="N108" s="18" t="n"/>
-      <c r="O108" s="18" t="n"/>
-      <c r="P108" s="18" t="n"/>
-      <c r="Q108" s="18" t="n"/>
-      <c r="R108" s="18" t="n"/>
-      <c r="S108" s="18" t="n"/>
-      <c r="T108" s="18" t="n"/>
-      <c r="U108" s="18" t="n"/>
-      <c r="V108" s="18" t="n"/>
-      <c r="W108" s="18" t="n"/>
-      <c r="X108" s="18" t="n"/>
-      <c r="Y108" s="18" t="n"/>
-      <c r="Z108" s="18" t="n"/>
-      <c r="AA108" s="18" t="n"/>
-      <c r="AB108" s="18" t="n"/>
-      <c r="AC108" s="18" t="n"/>
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="n">
+        <v>-39.193</v>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>-33</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="F108" s="22" t="n">
+        <v>-67</v>
+      </c>
+      <c r="G108" s="22" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H108" s="22" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I108" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="J108" s="22" t="n">
+        <v>-69</v>
+      </c>
+      <c r="K108" s="22" t="n">
+        <v>-43</v>
+      </c>
+      <c r="L108" s="22" t="n">
+        <v>-22</v>
+      </c>
+      <c r="M108" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N108" s="22" t="n">
+        <v>-67</v>
+      </c>
+      <c r="V108" s="22" t="n">
+        <v>-39.193</v>
+      </c>
+      <c r="W108" s="22" t="n">
+        <v>-13</v>
+      </c>
+      <c r="X108" s="22" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>2023.4Q</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>2024.1Q</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="M109" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="N109" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="O109" s="5" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="P109" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="Q109" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="R109" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="S109" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="T109" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U109" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V109" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="W109" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="X109" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Y109" s="5" t="inlineStr">
-        <is>
-          <t>2026(MW)</t>
-        </is>
-      </c>
-      <c r="Z109" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="AA109" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AB109" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AC109" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n">
+        <v>10.865</v>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>265</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>158</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>264</v>
+      </c>
+      <c r="G109" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H109" s="22" t="n">
+        <v>179</v>
+      </c>
+      <c r="I109" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>282</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <v>93</v>
+      </c>
+      <c r="L109" s="22" t="n">
+        <v>341</v>
+      </c>
+      <c r="M109" s="22" t="n">
+        <v>308</v>
+      </c>
+      <c r="N109" s="22" t="n">
+        <v>372</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>10.865</v>
+      </c>
+      <c r="W109" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="X109" s="22" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="110">
@@ -7377,1873 +7386,2049 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="inlineStr">
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G111" s="17">
+        <f>IF(OR(G110="",C110=""),"",IF(C110&lt;=0,"",IFERROR(G110/C110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H111" s="17">
+        <f>IF(OR(H110="",D110=""),"",IF(D110&lt;=0,"",IFERROR(H110/D110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I111" s="17">
+        <f>IF(OR(I110="",E110=""),"",IF(E110&lt;=0,"",IFERROR(I110/E110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J111" s="17">
+        <f>IF(OR(J110="",F110=""),"",IF(F110&lt;=0,"",IFERROR(J110/F110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF(OR(K110="",G110=""),"",IF(G110&lt;=0,"",IFERROR(K110/G110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L111" s="17">
+        <f>IF(OR(L110="",H110=""),"",IF(H110&lt;=0,"",IFERROR(L110/H110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M111" s="17">
+        <f>IF(OR(M110="",I110=""),"",IF(I110&lt;=0,"",IFERROR(M110/I110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N111" s="17">
+        <f>IF(OR(N110="",J110=""),"",IF(J110&lt;=0,"",IFERROR(N110/J110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V111" s="17">
+        <f>IF(OR(V110="",U110=""),"",IF(U110&lt;=0,"",IFERROR(V110/U110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W111" s="17">
+        <f>IF(OR(W110="",V110=""),"",IF(V110&lt;=0,"",IFERROR(W110/V110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X111" s="17">
+        <f>IF(OR(X110="",W110=""),"",IF(W110&lt;=0,"",IFERROR(X110/W110-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>265.259</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>527</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>296</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>546</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>346</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>373</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>468</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>578</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>550</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>693</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>596</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>265.259</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>346</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G113" s="17">
+        <f>IF(OR(G112="",C112=""),"",IF(C112&lt;=0,"",IFERROR(G112/C112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H113" s="17">
+        <f>IF(OR(H112="",D112=""),"",IF(D112&lt;=0,"",IFERROR(H112/D112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I113" s="17">
+        <f>IF(OR(I112="",E112=""),"",IF(E112&lt;=0,"",IFERROR(I112/E112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J113" s="17">
+        <f>IF(OR(J112="",F112=""),"",IF(F112&lt;=0,"",IFERROR(J112/F112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF(OR(K112="",G112=""),"",IF(G112&lt;=0,"",IFERROR(K112/G112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L113" s="17">
+        <f>IF(OR(L112="",H112=""),"",IF(H112&lt;=0,"",IFERROR(L112/H112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M113" s="17">
+        <f>IF(OR(M112="",I112=""),"",IF(I112&lt;=0,"",IFERROR(M112/I112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N113" s="17">
+        <f>IF(OR(N112="",J112=""),"",IF(J112&lt;=0,"",IFERROR(N112/J112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V113" s="17">
+        <f>IF(OR(V112="",U112=""),"",IF(U112&lt;=0,"",IFERROR(V112/U112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W113" s="17">
+        <f>IF(OR(W112="",V112=""),"",IF(V112&lt;=0,"",IFERROR(W112/V112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X113" s="17">
+        <f>IF(OR(X112="",W112=""),"",IF(W112&lt;=0,"",IFERROR(X112/W112-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B115" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+      <c r="J115" s="18" t="n"/>
+      <c r="K115" s="18" t="n"/>
+      <c r="L115" s="18" t="n"/>
+      <c r="M115" s="18" t="n"/>
+      <c r="N115" s="18" t="n"/>
+      <c r="O115" s="18" t="n"/>
+      <c r="P115" s="18" t="n"/>
+      <c r="Q115" s="18" t="n"/>
+      <c r="R115" s="18" t="n"/>
+      <c r="S115" s="18" t="n"/>
+      <c r="T115" s="18" t="n"/>
+      <c r="U115" s="18" t="n"/>
+      <c r="V115" s="18" t="n"/>
+      <c r="W115" s="18" t="n"/>
+      <c r="X115" s="18" t="n"/>
+      <c r="Y115" s="18" t="n"/>
+      <c r="Z115" s="18" t="n"/>
+      <c r="AA115" s="18" t="n"/>
+      <c r="AB115" s="18" t="n"/>
+      <c r="AC115" s="18" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>2023.4Q</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>2024.1Q</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q116" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="S116" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="T116" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U116" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="V116" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="W116" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="X116" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Y116" s="5" t="inlineStr">
+        <is>
+          <t>2026(MW)</t>
+        </is>
+      </c>
+      <c r="Z116" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="AA116" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AB116" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AC116" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>265.259</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>527</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>296</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>546</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>346</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>373</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>468</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>578</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>550</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>693</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>596</v>
+      </c>
+      <c r="N117" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="V117" s="12" t="n">
+        <v>265.259</v>
+      </c>
+      <c r="W117" s="12" t="n">
+        <v>346</v>
+      </c>
+      <c r="X117" s="12" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C111" s="22" t="n">
+      <c r="C118" s="22" t="n">
         <v>1.015</v>
       </c>
-      <c r="D111" s="22" t="n">
+      <c r="D118" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="E111" s="22" t="n">
+      <c r="E118" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="F111" s="22" t="n">
+      <c r="F118" s="22" t="n">
         <v>-4</v>
       </c>
-      <c r="G111" s="22" t="n">
+      <c r="G118" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H111" s="22" t="n">
+      <c r="H118" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="I111" s="22" t="n">
+      <c r="I118" s="22" t="n">
         <v>-26</v>
       </c>
-      <c r="J111" s="22" t="n">
+      <c r="J118" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K111" s="22" t="n">
+      <c r="K118" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="L111" s="22" t="n">
+      <c r="L118" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="M111" s="22" t="n">
+      <c r="M118" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="N111" s="22" t="n">
+      <c r="N118" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="V111" s="22" t="n">
+      <c r="V118" s="22" t="n">
         <v>1.015</v>
       </c>
-      <c r="W111" s="22" t="n">
+      <c r="W118" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="X111" s="22" t="n">
+      <c r="X118" s="22" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="C112" s="22" t="n">
+      <c r="C119" s="22" t="n">
         <v>1.015</v>
       </c>
-      <c r="D112" s="22" t="n">
+      <c r="D119" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="E112" s="22" t="n">
+      <c r="E119" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="F112" s="22" t="n">
+      <c r="F119" s="22" t="n">
         <v>-4</v>
       </c>
-      <c r="G112" s="22" t="n">
+      <c r="G119" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H112" s="22" t="n">
+      <c r="H119" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="I112" s="22" t="n">
+      <c r="I119" s="22" t="n">
         <v>-26</v>
       </c>
-      <c r="J112" s="22" t="n">
+      <c r="J119" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K112" s="22" t="n">
+      <c r="K119" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="L112" s="22" t="n">
+      <c r="L119" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="M112" s="22" t="n">
+      <c r="M119" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="N112" s="22" t="n">
+      <c r="N119" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="V112" s="22" t="n">
+      <c r="V119" s="22" t="n">
         <v>1.015</v>
       </c>
-      <c r="W112" s="22" t="n">
+      <c r="W119" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="X112" s="22" t="n">
+      <c r="X119" s="22" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C113" s="12" t="n">
+      <c r="C120" s="12" t="n">
         <v>266.274</v>
       </c>
-      <c r="D113" s="12" t="n">
+      <c r="D120" s="12" t="n">
         <v>536</v>
       </c>
-      <c r="E113" s="12" t="n">
+      <c r="E120" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="F113" s="12" t="n">
+      <c r="F120" s="12" t="n">
         <v>542</v>
       </c>
-      <c r="G113" s="12" t="n">
+      <c r="G120" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="H113" s="12" t="n">
+      <c r="H120" s="12" t="n">
         <v>399</v>
       </c>
-      <c r="I113" s="12" t="n">
+      <c r="I120" s="12" t="n">
         <v>442</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="J120" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="K113" s="12" t="n">
+      <c r="K120" s="12" t="n">
         <v>559</v>
       </c>
-      <c r="L113" s="12" t="n">
+      <c r="L120" s="12" t="n">
         <v>713</v>
       </c>
-      <c r="M113" s="12" t="n">
+      <c r="M120" s="12" t="n">
         <v>597</v>
       </c>
-      <c r="N113" s="12" t="n">
+      <c r="N120" s="12" t="n">
         <v>778</v>
       </c>
-      <c r="V113" s="12" t="n">
+      <c r="V120" s="12" t="n">
         <v>266.274</v>
       </c>
-      <c r="W113" s="12" t="n">
+      <c r="W120" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="X113" s="12" t="n">
+      <c r="X120" s="12" t="n">
         <v>559</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C114" s="12" t="n">
+      <c r="C121" s="12" t="n">
         <v>266.274</v>
       </c>
-      <c r="D114" s="12" t="n">
+      <c r="D121" s="12" t="n">
         <v>536</v>
       </c>
-      <c r="E114" s="12" t="n">
+      <c r="E121" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="F114" s="12" t="n">
+      <c r="F121" s="12" t="n">
         <v>542</v>
       </c>
-      <c r="G114" s="12" t="n">
+      <c r="G121" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H121" s="12" t="n">
         <v>399</v>
       </c>
-      <c r="I114" s="12" t="n">
+      <c r="I121" s="12" t="n">
         <v>442</v>
       </c>
-      <c r="J114" s="12" t="n">
+      <c r="J121" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="K114" s="12" t="n">
+      <c r="K121" s="12" t="n">
         <v>559</v>
       </c>
-      <c r="L114" s="12" t="n">
+      <c r="L121" s="12" t="n">
         <v>713</v>
       </c>
-      <c r="M114" s="12" t="n">
+      <c r="M121" s="12" t="n">
         <v>597</v>
       </c>
-      <c r="N114" s="12" t="n">
+      <c r="N121" s="12" t="n">
         <v>778</v>
       </c>
-      <c r="V114" s="12" t="n">
+      <c r="V121" s="12" t="n">
         <v>266.274</v>
       </c>
-      <c r="W114" s="12" t="n">
+      <c r="W121" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="X114" s="12" t="n">
+      <c r="X121" s="12" t="n">
         <v>559</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
+      <c r="C122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B117" s="44" t="inlineStr">
+      <c r="B124" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="18" t="n"/>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="18" t="n"/>
-      <c r="I117" s="18" t="n"/>
-      <c r="J117" s="18" t="n"/>
-      <c r="K117" s="18" t="n"/>
-      <c r="L117" s="18" t="n"/>
-      <c r="M117" s="18" t="n"/>
-      <c r="N117" s="18" t="n"/>
-      <c r="O117" s="18" t="n"/>
-      <c r="P117" s="18" t="n"/>
-      <c r="Q117" s="18" t="n"/>
-      <c r="R117" s="18" t="n"/>
-      <c r="S117" s="18" t="n"/>
-      <c r="T117" s="18" t="n"/>
-      <c r="U117" s="18" t="n"/>
-      <c r="V117" s="18" t="n"/>
-      <c r="W117" s="18" t="n"/>
-      <c r="X117" s="18" t="n"/>
-      <c r="Y117" s="18" t="n"/>
-      <c r="Z117" s="18" t="n"/>
-      <c r="AA117" s="18" t="n"/>
-      <c r="AB117" s="18" t="n"/>
-      <c r="AC117" s="18" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="C124" s="18" t="n"/>
+      <c r="D124" s="18" t="n"/>
+      <c r="E124" s="18" t="n"/>
+      <c r="F124" s="18" t="n"/>
+      <c r="G124" s="18" t="n"/>
+      <c r="H124" s="18" t="n"/>
+      <c r="I124" s="18" t="n"/>
+      <c r="J124" s="18" t="n"/>
+      <c r="K124" s="18" t="n"/>
+      <c r="L124" s="18" t="n"/>
+      <c r="M124" s="18" t="n"/>
+      <c r="N124" s="18" t="n"/>
+      <c r="O124" s="18" t="n"/>
+      <c r="P124" s="18" t="n"/>
+      <c r="Q124" s="18" t="n"/>
+      <c r="R124" s="18" t="n"/>
+      <c r="S124" s="18" t="n"/>
+      <c r="T124" s="18" t="n"/>
+      <c r="U124" s="18" t="n"/>
+      <c r="V124" s="18" t="n"/>
+      <c r="W124" s="18" t="n"/>
+      <c r="X124" s="18" t="n"/>
+      <c r="Y124" s="18" t="n"/>
+      <c r="Z124" s="18" t="n"/>
+      <c r="AA124" s="18" t="n"/>
+      <c r="AB124" s="18" t="n"/>
+      <c r="AC124" s="18" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>2023.4Q</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>2024.1Q</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J125" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr">
+      <c r="K125" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
+      <c r="L125" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="M118" s="5" t="inlineStr">
+      <c r="M125" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="N118" s="5" t="inlineStr">
+      <c r="N125" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="O118" s="5" t="inlineStr">
+      <c r="O125" s="5" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="P118" s="5" t="inlineStr">
+      <c r="P125" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="Q118" s="5" t="inlineStr">
+      <c r="Q125" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="R118" s="5" t="inlineStr">
+      <c r="R125" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="S118" s="5" t="inlineStr">
+      <c r="S125" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="T118" s="5" t="inlineStr">
+      <c r="T125" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="U118" s="5" t="inlineStr">
+      <c r="U125" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V118" s="5" t="inlineStr">
+      <c r="V125" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="W118" s="5" t="inlineStr">
+      <c r="W125" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="X118" s="5" t="inlineStr">
+      <c r="X125" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="Y118" s="5" t="inlineStr">
+      <c r="Y125" s="5" t="inlineStr">
         <is>
           <t>2026(MW)</t>
         </is>
       </c>
-      <c r="Z118" s="5" t="inlineStr">
+      <c r="Z125" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="AA118" s="5" t="inlineStr">
+      <c r="AA125" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AB118" s="5" t="inlineStr">
+      <c r="AB125" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AC118" s="5" t="inlineStr">
+      <c r="AC125" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C119" s="12" t="n">
+      <c r="C126" s="12" t="n">
         <v>1449.523</v>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="E126" s="12" t="n">
         <v>1247</v>
       </c>
-      <c r="G119" s="12" t="n">
+      <c r="G126" s="12" t="n">
         <v>2415</v>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="I126" s="12" t="n">
         <v>1257</v>
       </c>
-      <c r="K119" s="12" t="n">
+      <c r="K126" s="12" t="n">
         <v>2760</v>
       </c>
-      <c r="M119" s="12" t="n">
+      <c r="M126" s="12" t="n">
         <v>1939</v>
       </c>
-      <c r="O119" s="12" t="n">
+      <c r="O126" s="12" t="n">
         <v>2775.43</v>
       </c>
-      <c r="P119" s="12" t="n">
+      <c r="P126" s="12" t="n">
         <v>2483.996</v>
       </c>
-      <c r="Q119" s="12" t="n">
+      <c r="Q126" s="12" t="n">
         <v>2579.027</v>
       </c>
-      <c r="R119" s="12" t="n">
+      <c r="R126" s="12" t="n">
         <v>2325.883</v>
       </c>
-      <c r="S119" s="12" t="n">
+      <c r="S126" s="12" t="n">
         <v>-413.66</v>
       </c>
-      <c r="T119" s="12" t="n">
+      <c r="T126" s="12" t="n">
         <v>1425.136</v>
       </c>
-      <c r="U119" s="12" t="n">
+      <c r="U126" s="12" t="n">
         <v>1034.038</v>
       </c>
-      <c r="V119" s="12" t="n">
+      <c r="V126" s="12" t="n">
         <v>1449.523</v>
       </c>
-      <c r="W119" s="12" t="n">
+      <c r="W126" s="12" t="n">
         <v>2415</v>
       </c>
-      <c r="X119" s="12" t="n">
+      <c r="X126" s="12" t="n">
         <v>2760</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C120" s="22" t="n">
-        <v>869.484</v>
-      </c>
-      <c r="E120" s="22" t="n">
-        <v>415</v>
-      </c>
-      <c r="G120" s="22" t="n">
-        <v>875</v>
-      </c>
-      <c r="I120" s="22" t="n">
-        <v>443</v>
-      </c>
-      <c r="K120" s="22" t="n">
-        <v>932</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <v>468</v>
-      </c>
-      <c r="O120" s="22" t="n">
-        <v>778.432</v>
-      </c>
-      <c r="P120" s="22" t="n">
-        <v>822.775</v>
-      </c>
-      <c r="Q120" s="22" t="n">
-        <v>922.426</v>
-      </c>
-      <c r="R120" s="22" t="n">
-        <v>912.234</v>
-      </c>
-      <c r="S120" s="22" t="n">
-        <v>820.3920000000001</v>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>783.453</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>825.125</v>
-      </c>
-      <c r="V120" s="22" t="n">
-        <v>869.484</v>
-      </c>
-      <c r="W120" s="22" t="n">
-        <v>875</v>
-      </c>
-      <c r="X120" s="22" t="n">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="C121" s="22" t="n">
-        <v>227.461</v>
-      </c>
-      <c r="E121" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="22" t="n">
-        <v>176</v>
-      </c>
-      <c r="K121" s="22" t="n">
-        <v>261</v>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="22" t="n">
-        <v>27.503</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>76.04000000000001</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>118.621</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>508.04</v>
-      </c>
-      <c r="T121" s="22" t="n">
-        <v>70.22</v>
-      </c>
-      <c r="U121" s="22" t="n">
-        <v>57.294</v>
-      </c>
-      <c r="V121" s="22" t="n">
-        <v>227.461</v>
-      </c>
-      <c r="W121" s="22" t="n">
-        <v>176</v>
-      </c>
-      <c r="X121" s="22" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C122" s="22" t="n">
-        <v>5.455</v>
-      </c>
-      <c r="E122" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G122" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I122" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K122" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M122" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V122" s="22" t="n">
-        <v>5.455</v>
-      </c>
-      <c r="W122" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="X122" s="22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C123" s="22" t="n">
-        <v>5.914</v>
-      </c>
-      <c r="E123" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="G123" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="K123" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M123" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="O123" s="22" t="n">
-        <v>6.296</v>
-      </c>
-      <c r="P123" s="22" t="n">
-        <v>3.828</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>-0.9389999999999999</v>
-      </c>
-      <c r="T123" s="22" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>2.579</v>
-      </c>
-      <c r="V123" s="22" t="n">
-        <v>5.914</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>판매촉진 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C124" s="22" t="n">
-        <v>21.588</v>
-      </c>
-      <c r="E124" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G124" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K124" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O124" s="22" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="P124" s="22" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="Q124" s="22" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>43.315</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>15.203</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>-4.662</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>21.588</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>주주우대 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K125" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M125" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="C126" s="22" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="E126" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V126" s="22" t="n">
-        <v>-0.004</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
-        <v>-7.715</v>
+        <v>869.484</v>
       </c>
       <c r="E127" s="22" t="n">
-        <v>-4</v>
+        <v>415</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>-11</v>
+        <v>875</v>
       </c>
       <c r="I127" s="22" t="n">
-        <v>-7</v>
+        <v>443</v>
       </c>
       <c r="K127" s="22" t="n">
-        <v>-16</v>
+        <v>932</v>
       </c>
       <c r="M127" s="22" t="n">
-        <v>-9</v>
+        <v>468</v>
       </c>
       <c r="O127" s="22" t="n">
-        <v>-6.411</v>
+        <v>778.432</v>
       </c>
       <c r="P127" s="22" t="n">
-        <v>-5.517</v>
+        <v>822.775</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>-5.302</v>
+        <v>922.426</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>-5.774</v>
+        <v>912.234</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>-7.428</v>
+        <v>820.3920000000001</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>-7.198</v>
+        <v>783.453</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>-8.287000000000001</v>
+        <v>825.125</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>-7.715</v>
+        <v>869.484</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>-11</v>
+        <v>875</v>
       </c>
       <c r="X127" s="22" t="n">
-        <v>-16</v>
+        <v>932</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C128" s="22" t="n">
-        <v>0.737</v>
+        <v>227.461</v>
       </c>
       <c r="E128" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="K128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="O128" s="22" t="n">
-        <v>0.489</v>
+        <v>0</v>
       </c>
       <c r="P128" s="22" t="n">
-        <v>0.383</v>
+        <v>27.503</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>0.401</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="R128" s="22" t="n">
-        <v>0.472</v>
+        <v>118.621</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>6.271</v>
+        <v>508.04</v>
       </c>
       <c r="T128" s="22" t="n">
-        <v>10.115</v>
+        <v>70.22</v>
       </c>
       <c r="U128" s="22" t="n">
-        <v>3.899</v>
+        <v>57.294</v>
       </c>
       <c r="V128" s="22" t="n">
-        <v>0.737</v>
+        <v>227.461</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>-1538.864</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>-237.569</v>
+          <t>영업권 상각</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="E129" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I129" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V129" s="22" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="W129" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="X129" s="22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>보험금 수익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C130" s="22" t="n">
+        <v>5.914</v>
+      </c>
+      <c r="E130" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G130" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I130" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K130" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M130" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="O130" s="22" t="n">
+        <v>6.296</v>
+      </c>
+      <c r="P130" s="22" t="n">
+        <v>3.828</v>
+      </c>
+      <c r="Q130" s="22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R130" s="22" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="S130" s="22" t="n">
+        <v>-0.9389999999999999</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>0</v>
+        <v>1.533</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-86.14100000000001</v>
+        <v>2.579</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>5.914</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
+          <t>판매촉진 충당금 증감</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n">
+        <v>21.588</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="M131" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" s="22" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="P131" s="22" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="Q131" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>0.075</v>
       </c>
       <c r="S131" s="22" t="n">
-        <v>-115.81</v>
+        <v>43.315</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>-21.927</v>
+        <v>15.203</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>0</v>
+        <v>-4.662</v>
+      </c>
+      <c r="V131" s="22" t="n">
+        <v>21.588</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="X131" s="22" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각손익</t>
-        </is>
+          <t>주주우대 충당금 증감</t>
+        </is>
+      </c>
+      <c r="C132" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E132" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I132" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K132" s="22" t="n">
         <v>-0</v>
       </c>
-      <c r="K132" s="22" t="n">
-        <v>-24</v>
-      </c>
       <c r="M132" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V132" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>-24</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손익</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
-        <v>28.672</v>
+        <v>-0.004</v>
       </c>
       <c r="E133" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="22" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="I133" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K133" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M133" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O133" s="22" t="n">
-        <v>28.471</v>
-      </c>
-      <c r="P133" s="22" t="n">
-        <v>5.423</v>
-      </c>
-      <c r="Q133" s="22" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="R133" s="22" t="n">
-        <v>6.088</v>
-      </c>
-      <c r="S133" s="22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="T133" s="22" t="n">
-        <v>4.261</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>16.226</v>
+        <v>-0</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>28.672</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>3</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 상환손익</t>
-        </is>
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>-7.715</v>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I134" s="22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M134" s="22" t="n">
+        <v>-9</v>
       </c>
       <c r="O134" s="22" t="n">
-        <v>3.502</v>
+        <v>-6.411</v>
       </c>
       <c r="P134" s="22" t="n">
-        <v>0</v>
+        <v>-5.517</v>
+      </c>
+      <c r="Q134" s="22" t="n">
+        <v>-5.302</v>
+      </c>
+      <c r="R134" s="22" t="n">
+        <v>-5.774</v>
+      </c>
+      <c r="S134" s="22" t="n">
+        <v>-7.428</v>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>-7.198</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>-8.287000000000001</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>-7.715</v>
+      </c>
+      <c r="W134" s="22" t="n">
+        <v>-11</v>
+      </c>
+      <c r="X134" s="22" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>화재손실</t>
-        </is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="22" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="P135" s="22" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="Q135" s="22" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="R135" s="22" t="n">
+        <v>0.472</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>0</v>
+        <v>6.271</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>40.335</v>
+        <v>10.115</v>
       </c>
       <c r="U135" s="22" t="n">
+        <v>3.899</v>
+      </c>
+      <c r="V135" s="22" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="W135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="Q136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" s="22" t="n">
-        <v>8.096</v>
+          <t>보조금 수입</t>
+        </is>
       </c>
       <c r="S136" s="22" t="n">
-        <v>12.809</v>
+        <v>0</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>0</v>
+        <v>-1538.864</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>-237.569</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="C137" s="22" t="n">
-        <v>-85.267</v>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="G137" s="22" t="n">
-        <v>-70</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K137" s="22" t="n">
-        <v>-328</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>102</v>
-      </c>
-      <c r="O137" s="22" t="n">
-        <v>3.602</v>
-      </c>
-      <c r="P137" s="22" t="n">
-        <v>-51.688</v>
-      </c>
-      <c r="Q137" s="22" t="n">
-        <v>-37.184</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>-87.828</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>-136.194</v>
+          <t>보험금 수익</t>
+        </is>
       </c>
       <c r="T137" s="22" t="n">
-        <v>-245.766</v>
+        <v>0</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-14.815</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>-85.267</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>-70</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>-328</v>
+        <v>-86.14100000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="C138" s="22" t="n">
-        <v>-116.645</v>
-      </c>
-      <c r="E138" s="22" t="n">
-        <v>-239</v>
-      </c>
-      <c r="G138" s="22" t="n">
-        <v>-310</v>
-      </c>
-      <c r="I138" s="22" t="n">
-        <v>508</v>
-      </c>
-      <c r="K138" s="22" t="n">
-        <v>229</v>
-      </c>
-      <c r="M138" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="O138" s="22" t="n">
-        <v>-44.702</v>
-      </c>
-      <c r="P138" s="22" t="n">
-        <v>-35.963</v>
-      </c>
-      <c r="Q138" s="22" t="n">
-        <v>-192.332</v>
-      </c>
-      <c r="R138" s="22" t="n">
-        <v>-52.225</v>
+          <t>보조금 수입</t>
+        </is>
       </c>
       <c r="S138" s="22" t="n">
-        <v>301.264</v>
+        <v>-115.81</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>-16.102</v>
+        <v>-21.927</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>-244.072</v>
-      </c>
-      <c r="V138" s="22" t="n">
-        <v>-116.645</v>
-      </c>
-      <c r="W138" s="22" t="n">
-        <v>-310</v>
-      </c>
-      <c r="X138" s="22" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>선급비용 증감</t>
-        </is>
-      </c>
-      <c r="C139" s="22" t="n">
-        <v>-0.791</v>
+          <t>유가증권 매각손익</t>
+        </is>
       </c>
       <c r="E139" s="22" t="n">
-        <v>-88</v>
+        <v>0</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>-110</v>
+        <v>-0</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>-31</v>
+        <v>-24</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-114</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>-0.791</v>
+        <v>0</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-31</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>장기선급비용 증감</t>
+          <t>고정자산 제각·매각손익</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>-15.361</v>
+        <v>28.672</v>
+      </c>
+      <c r="E140" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I140" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="M140" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="O140" s="22" t="n">
-        <v>10.104</v>
+        <v>28.471</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>-23.303</v>
+        <v>5.423</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>6.162</v>
+        <v>14.36</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>13.691</v>
+        <v>6.088</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>-31.403</v>
+        <v>7.4</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>9.317</v>
+        <v>4.261</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>9.032</v>
+        <v>16.226</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-15.361</v>
+        <v>28.672</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="n">
-        <v>86.246</v>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>-52</v>
-      </c>
-      <c r="G141" s="22" t="n">
-        <v>-146</v>
-      </c>
-      <c r="I141" s="22" t="n">
-        <v>-22</v>
-      </c>
-      <c r="K141" s="22" t="n">
-        <v>104</v>
-      </c>
-      <c r="M141" s="22" t="n">
-        <v>-81</v>
+          <t>투자유가증권 상환손익</t>
+        </is>
       </c>
       <c r="O141" s="22" t="n">
-        <v>53.885</v>
+        <v>3.502</v>
       </c>
       <c r="P141" s="22" t="n">
-        <v>97.018</v>
-      </c>
-      <c r="Q141" s="22" t="n">
-        <v>18.091</v>
-      </c>
-      <c r="R141" s="22" t="n">
-        <v>-62.64</v>
-      </c>
-      <c r="S141" s="22" t="n">
-        <v>-131.302</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>125.511</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>194.343</v>
-      </c>
-      <c r="V141" s="22" t="n">
-        <v>86.246</v>
-      </c>
-      <c r="W141" s="22" t="n">
-        <v>-146</v>
-      </c>
-      <c r="X141" s="22" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
-        </is>
-      </c>
-      <c r="C142" s="22" t="n">
-        <v>86.114</v>
-      </c>
-      <c r="E142" s="22" t="n">
-        <v>359</v>
-      </c>
-      <c r="G142" s="22" t="n">
-        <v>224</v>
-      </c>
-      <c r="I142" s="22" t="n">
-        <v>186</v>
-      </c>
-      <c r="K142" s="22" t="n">
-        <v>196</v>
-      </c>
-      <c r="M142" s="22" t="n">
-        <v>361</v>
-      </c>
-      <c r="O142" s="22" t="n">
-        <v>63.775</v>
-      </c>
-      <c r="P142" s="22" t="n">
-        <v>102.783</v>
-      </c>
-      <c r="Q142" s="22" t="n">
-        <v>60.98</v>
-      </c>
-      <c r="R142" s="22" t="n">
-        <v>4.056</v>
+          <t>화재손실</t>
+        </is>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-86.145</v>
+        <v>0</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>96.831</v>
+        <v>40.335</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="V142" s="22" t="n">
-        <v>86.114</v>
-      </c>
-      <c r="W142" s="22" t="n">
-        <v>224</v>
-      </c>
-      <c r="X142" s="22" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
-        </is>
-      </c>
-      <c r="C143" s="22" t="n">
-        <v>52.002</v>
-      </c>
-      <c r="E143" s="22" t="n">
-        <v>26.279</v>
-      </c>
-      <c r="V143" s="22" t="n">
-        <v>52.002</v>
+          <t>투자유가증권 평가손익</t>
+        </is>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>8.096</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>12.809</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="C144" s="22" t="n">
+        <v>-85.267</v>
+      </c>
+      <c r="E144" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="G144" s="22" t="n">
+        <v>-70</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="K144" s="22" t="n">
+        <v>-328</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>-24.323</v>
+        <v>3.602</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-75.529</v>
+        <v>-51.688</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>67.532</v>
+        <v>-37.184</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>84.23399999999999</v>
+        <v>-87.828</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>-176.37</v>
+        <v>-136.194</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-50.203</v>
+        <v>-245.766</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>232.966</v>
+        <v>-14.815</v>
+      </c>
+      <c r="V144" s="22" t="n">
+        <v>-85.267</v>
+      </c>
+      <c r="W144" s="22" t="n">
+        <v>-70</v>
+      </c>
+      <c r="X144" s="22" t="n">
+        <v>-328</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>52.002</v>
+        <v>-116.645</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>26</v>
+        <v>-239</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>28</v>
+        <v>-310</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>36</v>
+        <v>508</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>102</v>
+        <v>58</v>
+      </c>
+      <c r="O145" s="22" t="n">
+        <v>-44.702</v>
+      </c>
+      <c r="P145" s="22" t="n">
+        <v>-35.963</v>
+      </c>
+      <c r="Q145" s="22" t="n">
+        <v>-192.332</v>
+      </c>
+      <c r="R145" s="22" t="n">
+        <v>-52.225</v>
+      </c>
+      <c r="S145" s="22" t="n">
+        <v>301.264</v>
+      </c>
+      <c r="T145" s="22" t="n">
+        <v>-16.102</v>
+      </c>
+      <c r="U145" s="22" t="n">
+        <v>-244.072</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>52.002</v>
+        <v>-116.645</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>28</v>
+        <v>-310</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>115</v>
+        <v>229</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>선급비용 증감</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
-        <v>176.598</v>
+        <v>-0.791</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>-136</v>
+        <v>-88</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>-98</v>
+        <v>-110</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>-61</v>
+        <v>-31</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>-23</v>
-      </c>
-      <c r="O146" s="22" t="n">
-        <v>14.039</v>
-      </c>
-      <c r="P146" s="22" t="n">
-        <v>76.212</v>
-      </c>
-      <c r="Q146" s="22" t="n">
-        <v>-44.11</v>
-      </c>
-      <c r="R146" s="22" t="n">
-        <v>52.427</v>
-      </c>
-      <c r="S146" s="22" t="n">
-        <v>-45.402</v>
-      </c>
-      <c r="T146" s="22" t="n">
-        <v>89.47799999999999</v>
-      </c>
-      <c r="U146" s="22" t="n">
-        <v>29.094</v>
+        <v>-114</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>176.598</v>
+        <v>-0.791</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-61</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>장기선급비용 증감</t>
         </is>
       </c>
       <c r="C147" s="22" t="n">
-        <v>2784.018</v>
-      </c>
-      <c r="E147" s="22" t="n">
-        <v>1583</v>
+        <v>-15.361</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>3304</v>
-      </c>
-      <c r="I147" s="22" t="n">
-        <v>2230</v>
+        <v>17</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>4210</v>
-      </c>
-      <c r="M147" s="22" t="n">
-        <v>2910</v>
+        <v>13</v>
       </c>
       <c r="O147" s="22" t="n">
-        <v>3663.089</v>
+        <v>10.104</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>3428.003</v>
+        <v>-23.303</v>
       </c>
       <c r="Q147" s="22" t="n">
-        <v>3468.294</v>
+        <v>6.162</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>3318.448</v>
+        <v>13.691</v>
       </c>
       <c r="S147" s="22" t="n">
-        <v>554.837</v>
+        <v>-31.403</v>
       </c>
       <c r="T147" s="22" t="n">
-        <v>791.3339999999999</v>
+        <v>9.317</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>1809.919</v>
+        <v>9.032</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>2784.018</v>
+        <v>-15.361</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>3304</v>
+        <v>17</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>4210</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>7.715</v>
+        <v>86.246</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>4</v>
+        <v>-52</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>11</v>
+        <v>-146</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>7</v>
+        <v>-22</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>9</v>
+        <v>-81</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>6.411</v>
+        <v>53.885</v>
       </c>
       <c r="P148" s="22" t="n">
-        <v>5.517</v>
+        <v>97.018</v>
       </c>
       <c r="Q148" s="22" t="n">
-        <v>5.302</v>
+        <v>18.091</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>5.774</v>
+        <v>-62.64</v>
       </c>
       <c r="S148" s="22" t="n">
-        <v>7.428</v>
+        <v>-131.302</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>7.198</v>
+        <v>125.511</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>8.287000000000001</v>
+        <v>194.343</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>7.715</v>
+        <v>86.246</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>11</v>
+        <v>-146</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="C149" s="22" t="n">
-        <v>-0.737</v>
+        <v>86.114</v>
       </c>
       <c r="E149" s="22" t="n">
-        <v>-0</v>
+        <v>359</v>
       </c>
       <c r="G149" s="22" t="n">
-        <v>-0</v>
+        <v>224</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>-0</v>
+        <v>186</v>
       </c>
       <c r="K149" s="22" t="n">
-        <v>-0</v>
+        <v>196</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>-0</v>
+        <v>361</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>-0.479</v>
+        <v>63.775</v>
       </c>
       <c r="P149" s="22" t="n">
-        <v>-0.382</v>
+        <v>102.783</v>
       </c>
       <c r="Q149" s="22" t="n">
-        <v>-0.402</v>
+        <v>60.98</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>-0.475</v>
+        <v>4.056</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>-6.845</v>
+        <v>-86.145</v>
       </c>
       <c r="T149" s="22" t="n">
-        <v>-10.086</v>
+        <v>96.831</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>-3.397</v>
+        <v>0.868</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>-0.737</v>
+        <v>86.114</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>-0</v>
+        <v>224</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>-0</v>
+        <v>196</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C150" s="22" t="n">
-        <v>-245.231</v>
+        <v>52.002</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-377</v>
-      </c>
-      <c r="G150" s="22" t="n">
-        <v>-647</v>
-      </c>
-      <c r="I150" s="22" t="n">
-        <v>-485</v>
-      </c>
-      <c r="K150" s="22" t="n">
-        <v>-859</v>
-      </c>
-      <c r="M150" s="22" t="n">
-        <v>-497</v>
-      </c>
-      <c r="O150" s="22" t="n">
-        <v>-899.38</v>
-      </c>
-      <c r="P150" s="22" t="n">
-        <v>-900.052</v>
-      </c>
-      <c r="Q150" s="22" t="n">
-        <v>-680.197</v>
-      </c>
-      <c r="R150" s="22" t="n">
-        <v>-903.569</v>
-      </c>
-      <c r="S150" s="22" t="n">
-        <v>-729.227</v>
-      </c>
-      <c r="T150" s="22" t="n">
-        <v>-29.581</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>-756.499</v>
+        <v>26.279</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-245.231</v>
-      </c>
-      <c r="W150" s="22" t="n">
-        <v>-647</v>
-      </c>
-      <c r="X150" s="22" t="n">
-        <v>-859</v>
+        <v>52.002</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
-        </is>
+          <t>미지급 소비세 증감</t>
+        </is>
+      </c>
+      <c r="I151" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M151" s="22" t="n">
+        <v>86</v>
+      </c>
+      <c r="O151" s="22" t="n">
+        <v>-24.323</v>
+      </c>
+      <c r="P151" s="22" t="n">
+        <v>-75.529</v>
+      </c>
+      <c r="Q151" s="22" t="n">
+        <v>67.532</v>
+      </c>
+      <c r="R151" s="22" t="n">
+        <v>84.23399999999999</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>0.08500000000000001</v>
+        <v>-176.37</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>341.264</v>
+        <v>-50.203</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>0</v>
+        <v>232.966</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
-        </is>
-      </c>
-      <c r="S152" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" s="22" t="n">
-        <v>1302.476</v>
-      </c>
-      <c r="U152" s="22" t="n">
-        <v>473.456</v>
+          <t>계약부채 증감</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="n">
+        <v>52.002</v>
+      </c>
+      <c r="E152" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="I152" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>115</v>
+      </c>
+      <c r="M152" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="V152" s="22" t="n">
+        <v>52.002</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C153" s="22" t="n">
+        <v>176.598</v>
+      </c>
+      <c r="E153" s="22" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I153" s="22" t="n">
+        <v>-98</v>
+      </c>
+      <c r="K153" s="22" t="n">
+        <v>-61</v>
+      </c>
+      <c r="M153" s="22" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O153" s="22" t="n">
+        <v>14.039</v>
+      </c>
+      <c r="P153" s="22" t="n">
+        <v>76.212</v>
+      </c>
+      <c r="Q153" s="22" t="n">
+        <v>-44.11</v>
+      </c>
+      <c r="R153" s="22" t="n">
+        <v>52.427</v>
+      </c>
+      <c r="S153" s="22" t="n">
+        <v>-45.402</v>
       </c>
       <c r="T153" s="22" t="n">
-        <v>0</v>
+        <v>89.47799999999999</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>89.45099999999999</v>
+        <v>29.094</v>
+      </c>
+      <c r="V153" s="22" t="n">
+        <v>176.598</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>-61</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="n">
+        <v>2784.018</v>
+      </c>
+      <c r="E154" s="22" t="n">
+        <v>1583</v>
+      </c>
+      <c r="G154" s="22" t="n">
+        <v>3304</v>
+      </c>
+      <c r="I154" s="22" t="n">
+        <v>2230</v>
+      </c>
+      <c r="K154" s="22" t="n">
+        <v>4210</v>
+      </c>
+      <c r="M154" s="22" t="n">
+        <v>2910</v>
+      </c>
+      <c r="O154" s="22" t="n">
+        <v>3663.089</v>
+      </c>
+      <c r="P154" s="22" t="n">
+        <v>3428.003</v>
+      </c>
+      <c r="Q154" s="22" t="n">
+        <v>3468.294</v>
+      </c>
+      <c r="R154" s="22" t="n">
+        <v>3318.448</v>
       </c>
       <c r="S154" s="22" t="n">
-        <v>115.81</v>
+        <v>554.837</v>
       </c>
       <c r="T154" s="22" t="n">
-        <v>18.979</v>
+        <v>791.3339999999999</v>
       </c>
       <c r="U154" s="22" t="n">
-        <v>0</v>
+        <v>1809.919</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>2784.018</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>3304</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>4210</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="n">
-        <v>2545.766</v>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>1209</v>
-      </c>
-      <c r="G155" s="12" t="n">
-        <v>2668</v>
-      </c>
-      <c r="I155" s="12" t="n">
-        <v>1752</v>
-      </c>
-      <c r="K155" s="12" t="n">
-        <v>3366</v>
-      </c>
-      <c r="M155" s="12" t="n">
-        <v>2422</v>
-      </c>
-      <c r="O155" s="12" t="n">
-        <v>2769.639</v>
-      </c>
-      <c r="P155" s="12" t="n">
-        <v>2533.086</v>
-      </c>
-      <c r="Q155" s="12" t="n">
-        <v>2792.996</v>
-      </c>
-      <c r="R155" s="12" t="n">
-        <v>2420.177</v>
-      </c>
-      <c r="S155" s="12" t="n">
-        <v>-57.912</v>
-      </c>
-      <c r="T155" s="12" t="n">
-        <v>2421.584</v>
-      </c>
-      <c r="U155" s="12" t="n">
-        <v>1621.218</v>
-      </c>
-      <c r="V155" s="12" t="n">
-        <v>2545.766</v>
-      </c>
-      <c r="W155" s="12" t="n">
-        <v>2668</v>
-      </c>
-      <c r="X155" s="12" t="n">
-        <v>3366</v>
+      <c r="A155" s="20" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="n">
+        <v>7.715</v>
+      </c>
+      <c r="E155" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G155" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K155" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="O155" s="22" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="P155" s="22" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="Q155" s="22" t="n">
+        <v>5.302</v>
+      </c>
+      <c r="R155" s="22" t="n">
+        <v>5.774</v>
+      </c>
+      <c r="S155" s="22" t="n">
+        <v>7.428</v>
+      </c>
+      <c r="T155" s="22" t="n">
+        <v>7.198</v>
+      </c>
+      <c r="U155" s="22" t="n">
+        <v>8.287000000000001</v>
+      </c>
+      <c r="V155" s="22" t="n">
+        <v>7.715</v>
+      </c>
+      <c r="W155" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C156" s="22" t="n">
-        <v>-1.799</v>
+        <v>-0.737</v>
       </c>
       <c r="E156" s="22" t="n">
         <v>-0</v>
       </c>
       <c r="G156" s="22" t="n">
-        <v>-1</v>
+        <v>-0</v>
       </c>
       <c r="I156" s="22" t="n">
         <v>-0</v>
@@ -9254,20 +9439,32 @@
       <c r="M156" s="22" t="n">
         <v>-0</v>
       </c>
+      <c r="O156" s="22" t="n">
+        <v>-0.479</v>
+      </c>
+      <c r="P156" s="22" t="n">
+        <v>-0.382</v>
+      </c>
       <c r="Q156" s="22" t="n">
-        <v>0</v>
+        <v>-0.402</v>
       </c>
       <c r="R156" s="22" t="n">
-        <v>-0.104</v>
+        <v>-0.475</v>
       </c>
       <c r="S156" s="22" t="n">
-        <v>0</v>
+        <v>-6.845</v>
+      </c>
+      <c r="T156" s="22" t="n">
+        <v>-10.086</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>-3.397</v>
       </c>
       <c r="V156" s="22" t="n">
-        <v>-1.799</v>
+        <v>-0.737</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>-1</v>
+        <v>-0</v>
       </c>
       <c r="X156" s="22" t="n">
         <v>-0</v>
@@ -9276,1285 +9473,1499 @@
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C157" s="22" t="n">
+        <v>-245.231</v>
       </c>
       <c r="E157" s="22" t="n">
-        <v>0</v>
+        <v>-377</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>0</v>
+        <v>-647</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>0</v>
+        <v>-485</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>25</v>
+        <v>-859</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>0</v>
+        <v>-497</v>
+      </c>
+      <c r="O157" s="22" t="n">
+        <v>-899.38</v>
+      </c>
+      <c r="P157" s="22" t="n">
+        <v>-900.052</v>
+      </c>
+      <c r="Q157" s="22" t="n">
+        <v>-680.197</v>
+      </c>
+      <c r="R157" s="22" t="n">
+        <v>-903.569</v>
+      </c>
+      <c r="S157" s="22" t="n">
+        <v>-729.227</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>0</v>
+        <v>-29.581</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>15.809</v>
+        <v>-756.499</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>-245.231</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>0</v>
+        <v>-647</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>25</v>
+        <v>-859</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>관계회사 주식 취득</t>
-        </is>
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="S158" s="22" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="T158" s="22" t="n">
-        <v>0</v>
+        <v>341.264</v>
       </c>
       <c r="U158" s="22" t="n">
-        <v>-121.163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>장기대여</t>
-        </is>
+          <t>보조금 수취</t>
+        </is>
+      </c>
+      <c r="S159" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T159" s="22" t="n">
-        <v>0</v>
+        <v>1302.476</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>-250</v>
+        <v>473.456</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>장기대여금 회수</t>
+          <t>보험금 수취</t>
         </is>
       </c>
       <c r="T160" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U160" s="22" t="n">
-        <v>21</v>
+        <v>89.45099999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="C161" s="22" t="n">
-        <v>-1057.12</v>
-      </c>
-      <c r="E161" s="22" t="n">
-        <v>-315</v>
-      </c>
-      <c r="G161" s="22" t="n">
-        <v>-1077</v>
-      </c>
-      <c r="I161" s="22" t="n">
-        <v>-653</v>
-      </c>
-      <c r="K161" s="22" t="n">
-        <v>-1427</v>
-      </c>
-      <c r="M161" s="22" t="n">
-        <v>-611</v>
-      </c>
-      <c r="O161" s="22" t="n">
-        <v>-1577.982</v>
-      </c>
-      <c r="P161" s="22" t="n">
-        <v>-3345.34</v>
-      </c>
-      <c r="Q161" s="22" t="n">
-        <v>-1649.15</v>
-      </c>
-      <c r="R161" s="22" t="n">
-        <v>-758.2140000000001</v>
+          <t>보조금 수취</t>
+        </is>
       </c>
       <c r="S161" s="22" t="n">
-        <v>-296.477</v>
+        <v>115.81</v>
       </c>
       <c r="T161" s="22" t="n">
-        <v>-1695.123</v>
+        <v>18.979</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>-1032.914</v>
-      </c>
-      <c r="V161" s="22" t="n">
-        <v>-1057.12</v>
-      </c>
-      <c r="W161" s="22" t="n">
-        <v>-1077</v>
-      </c>
-      <c r="X161" s="22" t="n">
-        <v>-1427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="20" t="inlineStr">
-        <is>
-          <t>유형자산 제각 지출</t>
-        </is>
-      </c>
-      <c r="O162" s="22" t="n">
-        <v>-5.51</v>
-      </c>
-      <c r="P162" s="22" t="n">
-        <v>-4.53</v>
-      </c>
-      <c r="Q162" s="22" t="n">
-        <v>-7.892</v>
-      </c>
-      <c r="R162" s="22" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="S162" s="22" t="n">
-        <v>-0.314</v>
-      </c>
-      <c r="T162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" s="22" t="n">
-        <v>-0.198</v>
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C162" s="12" t="n">
+        <v>2545.766</v>
+      </c>
+      <c r="E162" s="12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>2668</v>
+      </c>
+      <c r="I162" s="12" t="n">
+        <v>1752</v>
+      </c>
+      <c r="K162" s="12" t="n">
+        <v>3366</v>
+      </c>
+      <c r="M162" s="12" t="n">
+        <v>2422</v>
+      </c>
+      <c r="O162" s="12" t="n">
+        <v>2769.639</v>
+      </c>
+      <c r="P162" s="12" t="n">
+        <v>2533.086</v>
+      </c>
+      <c r="Q162" s="12" t="n">
+        <v>2792.996</v>
+      </c>
+      <c r="R162" s="12" t="n">
+        <v>2420.177</v>
+      </c>
+      <c r="S162" s="12" t="n">
+        <v>-57.912</v>
+      </c>
+      <c r="T162" s="12" t="n">
+        <v>2421.584</v>
+      </c>
+      <c r="U162" s="12" t="n">
+        <v>1621.218</v>
+      </c>
+      <c r="V162" s="12" t="n">
+        <v>2545.766</v>
+      </c>
+      <c r="W162" s="12" t="n">
+        <v>2668</v>
+      </c>
+      <c r="X162" s="12" t="n">
+        <v>3366</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="C163" s="22" t="n">
-        <v>0.185</v>
+        <v>-1.799</v>
+      </c>
+      <c r="E163" s="22" t="n">
+        <v>-0</v>
       </c>
       <c r="G163" s="22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I163" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K163" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M163" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q163" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R163" s="22" t="n">
-        <v>0.274</v>
+        <v>-0.104</v>
       </c>
       <c r="S163" s="22" t="n">
-        <v>2.557</v>
-      </c>
-      <c r="T163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" s="22" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>0.185</v>
+        <v>-1.799</v>
       </c>
       <c r="W163" s="22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
-        </is>
-      </c>
-      <c r="C164" s="22" t="n">
-        <v>-15.13</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="E164" s="22" t="n">
-        <v>-59</v>
+        <v>0</v>
       </c>
       <c r="G164" s="22" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="I164" s="22" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="K164" s="22" t="n">
-        <v>-12</v>
+        <v>25</v>
       </c>
       <c r="M164" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O164" s="22" t="n">
-        <v>-27.312</v>
-      </c>
-      <c r="P164" s="22" t="n">
-        <v>-62.449</v>
-      </c>
-      <c r="Q164" s="22" t="n">
-        <v>-10.613</v>
-      </c>
-      <c r="R164" s="22" t="n">
-        <v>-26.423</v>
-      </c>
-      <c r="S164" s="22" t="n">
-        <v>-59.194</v>
+        <v>0</v>
       </c>
       <c r="T164" s="22" t="n">
-        <v>-125.959</v>
+        <v>0</v>
       </c>
       <c r="U164" s="22" t="n">
-        <v>-20.177</v>
-      </c>
-      <c r="V164" s="22" t="n">
-        <v>-15.13</v>
+        <v>15.809</v>
       </c>
       <c r="W164" s="22" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="X164" s="22" t="n">
-        <v>-12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 이행 지출</t>
-        </is>
-      </c>
-      <c r="Q165" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" s="22" t="n">
-        <v>-10.536</v>
-      </c>
-      <c r="S165" s="22" t="n">
-        <v>-14.14</v>
+          <t>관계회사 주식 취득</t>
+        </is>
       </c>
       <c r="T165" s="22" t="n">
-        <v>-12.12</v>
+        <v>0</v>
       </c>
       <c r="U165" s="22" t="n">
-        <v>-9.007999999999999</v>
+        <v>-121.163</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>보증금 납입</t>
-        </is>
-      </c>
-      <c r="C166" s="22" t="n">
-        <v>-26.688</v>
-      </c>
-      <c r="E166" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G166" s="22" t="n">
-        <v>-41</v>
-      </c>
-      <c r="I166" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K166" s="22" t="n">
-        <v>-32</v>
-      </c>
-      <c r="M166" s="22" t="n">
-        <v>-14</v>
-      </c>
-      <c r="O166" s="22" t="n">
-        <v>-71.271</v>
-      </c>
-      <c r="P166" s="22" t="n">
-        <v>-122.632</v>
-      </c>
-      <c r="Q166" s="22" t="n">
-        <v>-42.93</v>
-      </c>
-      <c r="R166" s="22" t="n">
-        <v>-12.403</v>
-      </c>
-      <c r="S166" s="22" t="n">
-        <v>-4.605</v>
+          <t>장기대여</t>
+        </is>
       </c>
       <c r="T166" s="22" t="n">
-        <v>-47.395</v>
+        <v>0</v>
       </c>
       <c r="U166" s="22" t="n">
-        <v>-36.912</v>
-      </c>
-      <c r="V166" s="22" t="n">
-        <v>-26.688</v>
-      </c>
-      <c r="W166" s="22" t="n">
-        <v>-41</v>
-      </c>
-      <c r="X166" s="22" t="n">
-        <v>-32</v>
+        <v>-250</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>보증금 회수</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="G167" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="I167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="M167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" s="22" t="n">
-        <v>5.458</v>
-      </c>
-      <c r="P167" s="22" t="n">
-        <v>2.722</v>
-      </c>
-      <c r="Q167" s="22" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="R167" s="22" t="n">
-        <v>19.322</v>
-      </c>
-      <c r="S167" s="22" t="n">
-        <v>51.76</v>
+          <t>장기대여금 회수</t>
+        </is>
       </c>
       <c r="T167" s="22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="U167" s="22" t="n">
-        <v>17.224</v>
-      </c>
-      <c r="V167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="X167" s="22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>건설협력금 회수</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C168" s="22" t="n">
-        <v>24.675</v>
+        <v>-1057.12</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>6</v>
+        <v>-315</v>
       </c>
       <c r="G168" s="22" t="n">
-        <v>25</v>
+        <v>-1077</v>
       </c>
       <c r="I168" s="22" t="n">
-        <v>12</v>
+        <v>-653</v>
       </c>
       <c r="K168" s="22" t="n">
-        <v>30</v>
+        <v>-1427</v>
       </c>
       <c r="M168" s="22" t="n">
-        <v>12</v>
+        <v>-611</v>
       </c>
       <c r="O168" s="22" t="n">
-        <v>29.112</v>
+        <v>-1577.982</v>
       </c>
       <c r="P168" s="22" t="n">
-        <v>25.363</v>
+        <v>-3345.34</v>
       </c>
       <c r="Q168" s="22" t="n">
-        <v>24.892</v>
+        <v>-1649.15</v>
       </c>
       <c r="R168" s="22" t="n">
-        <v>22.808</v>
+        <v>-758.2140000000001</v>
       </c>
       <c r="S168" s="22" t="n">
-        <v>21.421</v>
+        <v>-296.477</v>
       </c>
       <c r="T168" s="22" t="n">
-        <v>22.857</v>
+        <v>-1695.123</v>
       </c>
       <c r="U168" s="22" t="n">
-        <v>26.409</v>
+        <v>-1032.914</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>24.675</v>
+        <v>-1057.12</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>25</v>
+        <v>-1077</v>
       </c>
       <c r="X168" s="22" t="n">
-        <v>30</v>
+        <v>-1427</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>보험적립금 적립</t>
+          <t>유형자산 제각 지출</t>
         </is>
       </c>
       <c r="O169" s="22" t="n">
-        <v>-3.651</v>
+        <v>-5.51</v>
       </c>
       <c r="P169" s="22" t="n">
-        <v>-3.651</v>
+        <v>-4.53</v>
       </c>
       <c r="Q169" s="22" t="n">
-        <v>-3.651</v>
+        <v>-7.892</v>
       </c>
       <c r="R169" s="22" t="n">
-        <v>-3.651</v>
+        <v>-0.88</v>
       </c>
       <c r="S169" s="22" t="n">
-        <v>-3.651</v>
+        <v>-0.314</v>
       </c>
       <c r="T169" s="22" t="n">
-        <v>-3.651</v>
+        <v>0</v>
       </c>
       <c r="U169" s="22" t="n">
-        <v>-3.651</v>
+        <v>-0.198</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>출자금 납입</t>
-        </is>
-      </c>
-      <c r="P170" s="22" t="n">
-        <v>-0.01</v>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="C170" s="22" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="G170" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="Q170" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" s="22" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="S170" s="22" t="n">
+        <v>2.557</v>
+      </c>
+      <c r="T170" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" s="22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="V170" s="22" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="W170" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X170" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>예수보증금 반환</t>
-        </is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="C171" s="22" t="n">
+        <v>-15.13</v>
+      </c>
+      <c r="E171" s="22" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G171" s="22" t="n">
+        <v>-70</v>
+      </c>
+      <c r="I171" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K171" s="22" t="n">
+        <v>-12</v>
+      </c>
+      <c r="M171" s="22" t="n">
+        <v>-5</v>
       </c>
       <c r="O171" s="22" t="n">
-        <v>0</v>
+        <v>-27.312</v>
       </c>
       <c r="P171" s="22" t="n">
-        <v>-5.89</v>
+        <v>-62.449</v>
       </c>
       <c r="Q171" s="22" t="n">
-        <v>-10.52</v>
+        <v>-10.613</v>
       </c>
       <c r="R171" s="22" t="n">
-        <v>-0.35</v>
+        <v>-26.423</v>
       </c>
       <c r="S171" s="22" t="n">
-        <v>-0.572</v>
+        <v>-59.194</v>
       </c>
       <c r="T171" s="22" t="n">
-        <v>-0.062</v>
+        <v>-125.959</v>
       </c>
       <c r="U171" s="22" t="n">
-        <v>0</v>
+        <v>-20.177</v>
+      </c>
+      <c r="V171" s="22" t="n">
+        <v>-15.13</v>
+      </c>
+      <c r="W171" s="22" t="n">
+        <v>-70</v>
+      </c>
+      <c r="X171" s="22" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>예수보증금 수입</t>
-        </is>
-      </c>
-      <c r="O172" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" s="22" t="n">
-        <v>12.98</v>
+          <t>자산복구부채 이행 지출</t>
+        </is>
       </c>
       <c r="Q172" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R172" s="22" t="n">
-        <v>5</v>
+        <v>-10.536</v>
       </c>
       <c r="S172" s="22" t="n">
-        <v>0.249</v>
+        <v>-14.14</v>
       </c>
       <c r="T172" s="22" t="n">
-        <v>0</v>
+        <v>-12.12</v>
+      </c>
+      <c r="U172" s="22" t="n">
+        <v>-9.007999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>출자금 회수</t>
-        </is>
+          <t>보증금 납입</t>
+        </is>
+      </c>
+      <c r="C173" s="22" t="n">
+        <v>-26.688</v>
+      </c>
+      <c r="E173" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G173" s="22" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I173" s="22" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K173" s="22" t="n">
+        <v>-32</v>
+      </c>
+      <c r="M173" s="22" t="n">
+        <v>-14</v>
       </c>
       <c r="O173" s="22" t="n">
-        <v>0</v>
+        <v>-71.271</v>
       </c>
       <c r="P173" s="22" t="n">
-        <v>-0.01</v>
+        <v>-122.632</v>
+      </c>
+      <c r="Q173" s="22" t="n">
+        <v>-42.93</v>
+      </c>
+      <c r="R173" s="22" t="n">
+        <v>-12.403</v>
       </c>
       <c r="S173" s="22" t="n">
-        <v>0</v>
+        <v>-4.605</v>
       </c>
       <c r="T173" s="22" t="n">
-        <v>0.02</v>
+        <v>-47.395</v>
       </c>
       <c r="U173" s="22" t="n">
-        <v>0</v>
+        <v>-36.912</v>
+      </c>
+      <c r="V173" s="22" t="n">
+        <v>-26.688</v>
+      </c>
+      <c r="W173" s="22" t="n">
+        <v>-41</v>
+      </c>
+      <c r="X173" s="22" t="n">
+        <v>-32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>건설협력금 지급</t>
+          <t>보증금 회수</t>
         </is>
       </c>
       <c r="C174" s="22" t="n">
-        <v>-16.2</v>
+        <v>0</v>
+      </c>
+      <c r="E174" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="G174" s="22" t="n">
-        <v>-14</v>
+        <v>13</v>
+      </c>
+      <c r="I174" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="K174" s="22" t="n">
-        <v>-22</v>
+        <v>8</v>
+      </c>
+      <c r="M174" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="O174" s="22" t="n">
-        <v>-18</v>
+        <v>5.458</v>
       </c>
       <c r="P174" s="22" t="n">
-        <v>-18</v>
+        <v>2.722</v>
       </c>
       <c r="Q174" s="22" t="n">
-        <v>-27</v>
+        <v>0.888</v>
       </c>
       <c r="R174" s="22" t="n">
-        <v>-36</v>
+        <v>19.322</v>
       </c>
       <c r="S174" s="22" t="n">
-        <v>-36</v>
+        <v>51.76</v>
       </c>
       <c r="T174" s="22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="U174" s="22" t="n">
-        <v>-48</v>
+        <v>17.224</v>
       </c>
       <c r="V174" s="22" t="n">
-        <v>-16.2</v>
+        <v>0</v>
       </c>
       <c r="W174" s="22" t="n">
-        <v>-14</v>
+        <v>13</v>
       </c>
       <c r="X174" s="22" t="n">
-        <v>-22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
+          <t>건설협력금 회수</t>
         </is>
       </c>
       <c r="C175" s="22" t="n">
-        <v>0</v>
+        <v>24.675</v>
       </c>
       <c r="E175" s="22" t="n">
-        <v>-1000</v>
+        <v>6</v>
       </c>
       <c r="G175" s="22" t="n">
-        <v>-1000</v>
+        <v>25</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K175" s="22" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="M175" s="22" t="n">
+        <v>12</v>
       </c>
       <c r="O175" s="22" t="n">
-        <v>-36.191</v>
+        <v>29.112</v>
       </c>
       <c r="P175" s="22" t="n">
-        <v>-36.123</v>
+        <v>25.363</v>
       </c>
       <c r="Q175" s="22" t="n">
-        <v>-36.083</v>
+        <v>24.892</v>
       </c>
       <c r="R175" s="22" t="n">
-        <v>-1036.082</v>
+        <v>22.808</v>
       </c>
       <c r="S175" s="22" t="n">
-        <v>-12.083</v>
+        <v>21.421</v>
       </c>
       <c r="T175" s="22" t="n">
-        <v>-0.046</v>
+        <v>22.857</v>
       </c>
       <c r="U175" s="22" t="n">
-        <v>-0.021</v>
+        <v>26.409</v>
       </c>
       <c r="V175" s="22" t="n">
-        <v>0</v>
+        <v>24.675</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>-1000</v>
+        <v>25</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 상환</t>
+          <t>보험적립금 적립</t>
         </is>
       </c>
       <c r="O176" s="22" t="n">
-        <v>7.831</v>
+        <v>-3.651</v>
       </c>
       <c r="P176" s="22" t="n">
-        <v>0</v>
+        <v>-3.651</v>
+      </c>
+      <c r="Q176" s="22" t="n">
+        <v>-3.651</v>
+      </c>
+      <c r="R176" s="22" t="n">
+        <v>-3.651</v>
+      </c>
+      <c r="S176" s="22" t="n">
+        <v>-3.651</v>
+      </c>
+      <c r="T176" s="22" t="n">
+        <v>-3.651</v>
+      </c>
+      <c r="U176" s="22" t="n">
+        <v>-3.651</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
-        </is>
-      </c>
-      <c r="C177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" s="22" t="n">
-        <v>973</v>
-      </c>
-      <c r="G177" s="22" t="n">
-        <v>981</v>
-      </c>
-      <c r="I177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" s="22" t="n">
-        <v>24.594</v>
-      </c>
-      <c r="U177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W177" s="22" t="n">
-        <v>981</v>
-      </c>
-      <c r="X177" s="22" t="n">
+          <t>출자금 납입</t>
+        </is>
+      </c>
+      <c r="P177" s="22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q177" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
-      </c>
-      <c r="C178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" s="22" t="n">
-        <v>-199</v>
-      </c>
-      <c r="G178" s="22" t="n">
-        <v>-199</v>
-      </c>
-      <c r="I178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" s="22" t="n">
-        <v>-72</v>
-      </c>
-      <c r="V178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W178" s="22" t="n">
-        <v>-199</v>
-      </c>
-      <c r="X178" s="22" t="n">
+          <t>예수보증금 반환</t>
+        </is>
+      </c>
+      <c r="O178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="22" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="Q178" s="22" t="n">
+        <v>-10.52</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="S178" s="22" t="n">
+        <v>-0.572</v>
+      </c>
+      <c r="T178" s="22" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="U178" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C179" s="22" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="E179" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G179" s="22" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I179" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K179" s="22" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M179" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V179" s="22" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="W179" s="22" t="n">
-        <v>-8</v>
-      </c>
-      <c r="X179" s="22" t="n">
-        <v>-4</v>
+          <t>예수보증금 수입</t>
+        </is>
+      </c>
+      <c r="O179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" s="22" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="Q179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S179" s="22" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="T179" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C180" s="12" t="n">
-        <v>-1087.958</v>
-      </c>
-      <c r="E180" s="12" t="n">
-        <v>-595</v>
-      </c>
-      <c r="G180" s="12" t="n">
-        <v>-1391</v>
-      </c>
-      <c r="I180" s="12" t="n">
-        <v>-668</v>
-      </c>
-      <c r="K180" s="12" t="n">
-        <v>-1436</v>
-      </c>
-      <c r="M180" s="12" t="n">
-        <v>-693</v>
-      </c>
-      <c r="O180" s="12" t="n">
-        <v>-1697.518</v>
-      </c>
-      <c r="P180" s="12" t="n">
-        <v>-3557.564</v>
-      </c>
-      <c r="Q180" s="12" t="n">
-        <v>-1762.062</v>
-      </c>
-      <c r="R180" s="12" t="n">
-        <v>-1837.24</v>
-      </c>
-      <c r="S180" s="12" t="n">
-        <v>-351.051</v>
-      </c>
-      <c r="T180" s="12" t="n">
-        <v>-1818.386</v>
-      </c>
-      <c r="U180" s="12" t="n">
-        <v>-1440.824</v>
-      </c>
-      <c r="V180" s="12" t="n">
-        <v>-1087.958</v>
-      </c>
-      <c r="W180" s="12" t="n">
-        <v>-1391</v>
-      </c>
-      <c r="X180" s="12" t="n">
-        <v>-1436</v>
+      <c r="A180" s="20" t="inlineStr">
+        <is>
+          <t>출자금 회수</t>
+        </is>
+      </c>
+      <c r="O180" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="S180" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" s="22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U180" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>건설협력금 지급</t>
         </is>
       </c>
       <c r="C181" s="22" t="n">
-        <v>-18.336</v>
-      </c>
-      <c r="E181" s="22" t="n">
-        <v>-3</v>
+        <v>-16.2</v>
       </c>
       <c r="G181" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I181" s="22" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="K181" s="22" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="O181" s="22" t="n">
-        <v>-0.54</v>
+        <v>-18</v>
       </c>
       <c r="P181" s="22" t="n">
-        <v>2.068</v>
+        <v>-18</v>
       </c>
       <c r="Q181" s="22" t="n">
-        <v>-4.884</v>
+        <v>-27</v>
       </c>
       <c r="R181" s="22" t="n">
-        <v>6.984</v>
+        <v>-36</v>
       </c>
       <c r="S181" s="22" t="n">
-        <v>-43.2</v>
+        <v>-36</v>
       </c>
       <c r="T181" s="22" t="n">
-        <v>-19.6</v>
+        <v>0</v>
       </c>
       <c r="U181" s="22" t="n">
-        <v>29.36</v>
+        <v>-48</v>
       </c>
       <c r="V181" s="22" t="n">
-        <v>-18.336</v>
+        <v>-16.2</v>
       </c>
       <c r="W181" s="22" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="X181" s="22" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
-        </is>
+          <t>정기예금 예입</t>
+        </is>
+      </c>
+      <c r="C182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="22" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="22" t="n">
+        <v>-36.191</v>
+      </c>
+      <c r="P182" s="22" t="n">
+        <v>-36.123</v>
+      </c>
+      <c r="Q182" s="22" t="n">
+        <v>-36.083</v>
       </c>
       <c r="R182" s="22" t="n">
-        <v>0</v>
+        <v>-1036.082</v>
       </c>
       <c r="S182" s="22" t="n">
-        <v>5000</v>
+        <v>-12.083</v>
       </c>
       <c r="T182" s="22" t="n">
-        <v>1000</v>
+        <v>-0.046</v>
       </c>
       <c r="U182" s="22" t="n">
-        <v>700</v>
+        <v>-0.021</v>
+      </c>
+      <c r="V182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" s="22" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="X182" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="C183" s="22" t="n">
-        <v>-348</v>
-      </c>
-      <c r="E183" s="22" t="n">
-        <v>-120</v>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T183" s="22" t="n">
-        <v>-199.992</v>
-      </c>
-      <c r="U183" s="22" t="n">
-        <v>-6032.008</v>
-      </c>
-      <c r="V183" s="22" t="n">
-        <v>-348</v>
-      </c>
-      <c r="W183" s="22" t="n">
-        <v>-202</v>
-      </c>
-      <c r="X183" s="22" t="n">
+          <t>투자유가증권 상환</t>
+        </is>
+      </c>
+      <c r="O183" s="22" t="n">
+        <v>7.831</v>
+      </c>
+      <c r="P183" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>정기예금 인출</t>
         </is>
       </c>
       <c r="C184" s="22" t="n">
-        <v>-20.132</v>
+        <v>0</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-15</v>
+        <v>973</v>
       </c>
       <c r="G184" s="22" t="n">
-        <v>-25</v>
+        <v>981</v>
       </c>
       <c r="I184" s="22" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="K184" s="22" t="n">
-        <v>-29</v>
-      </c>
-      <c r="M184" s="22" t="n">
-        <v>-14</v>
-      </c>
-      <c r="O184" s="22" t="n">
-        <v>-12.162</v>
-      </c>
-      <c r="P184" s="22" t="n">
-        <v>-12.662</v>
-      </c>
-      <c r="Q184" s="22" t="n">
-        <v>-14.228</v>
-      </c>
-      <c r="R184" s="22" t="n">
-        <v>-15.6</v>
+        <v>0</v>
       </c>
       <c r="S184" s="22" t="n">
-        <v>-16.95</v>
+        <v>0</v>
       </c>
       <c r="T184" s="22" t="n">
-        <v>-18.75</v>
+        <v>24.594</v>
       </c>
       <c r="U184" s="22" t="n">
-        <v>-19.9</v>
+        <v>0</v>
       </c>
       <c r="V184" s="22" t="n">
-        <v>-20.132</v>
+        <v>0</v>
       </c>
       <c r="W184" s="22" t="n">
-        <v>-25</v>
+        <v>981</v>
       </c>
       <c r="X184" s="22" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>연결범위 변경 자회사 주식 취득</t>
         </is>
       </c>
       <c r="C185" s="22" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E185" s="22" t="n">
-        <v>0</v>
+        <v>-199</v>
       </c>
       <c r="G185" s="22" t="n">
-        <v>-0</v>
+        <v>-199</v>
       </c>
       <c r="I185" s="22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K185" s="22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M185" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O185" s="22" t="n">
-        <v>-0.249</v>
-      </c>
-      <c r="P185" s="22" t="n">
-        <v>-0.234</v>
-      </c>
-      <c r="Q185" s="22" t="n">
-        <v>-0.392</v>
-      </c>
-      <c r="R185" s="22" t="n">
-        <v>-0.163</v>
-      </c>
-      <c r="S185" s="22" t="n">
-        <v>-0.192</v>
-      </c>
-      <c r="T185" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U185" s="22" t="n">
-        <v>-524.232</v>
+        <v>-72</v>
       </c>
       <c r="V185" s="22" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="W185" s="22" t="n">
-        <v>-0</v>
+        <v>-199</v>
       </c>
       <c r="X185" s="22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C186" s="22" t="n">
-        <v>-239.989</v>
+        <v>4.12</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>-146</v>
+        <v>-0</v>
       </c>
       <c r="G186" s="22" t="n">
-        <v>-324</v>
+        <v>-8</v>
       </c>
       <c r="I186" s="22" t="n">
-        <v>-180</v>
+        <v>-0</v>
       </c>
       <c r="K186" s="22" t="n">
-        <v>-373</v>
+        <v>-4</v>
       </c>
       <c r="M186" s="22" t="n">
-        <v>-223</v>
-      </c>
-      <c r="O186" s="22" t="n">
-        <v>-301.233</v>
-      </c>
-      <c r="P186" s="22" t="n">
-        <v>-346.273</v>
-      </c>
-      <c r="Q186" s="22" t="n">
-        <v>-361.718</v>
-      </c>
-      <c r="R186" s="22" t="n">
-        <v>-362.274</v>
-      </c>
-      <c r="S186" s="22" t="n">
-        <v>-181.482</v>
-      </c>
-      <c r="T186" s="22" t="n">
-        <v>-241.427</v>
-      </c>
-      <c r="U186" s="22" t="n">
-        <v>-269.994</v>
+        <v>-2</v>
       </c>
       <c r="V186" s="22" t="n">
-        <v>-239.989</v>
+        <v>4.12</v>
       </c>
       <c r="W186" s="22" t="n">
-        <v>-324</v>
+        <v>-8</v>
       </c>
       <c r="X186" s="22" t="n">
-        <v>-373</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" s="22" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" s="22" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="S187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W187" s="22" t="n">
-        <v>-8</v>
-      </c>
-      <c r="X187" s="22" t="n">
-        <v>0</v>
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="n">
+        <v>-1087.958</v>
+      </c>
+      <c r="E187" s="12" t="n">
+        <v>-595</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>-1391</v>
+      </c>
+      <c r="I187" s="12" t="n">
+        <v>-668</v>
+      </c>
+      <c r="K187" s="12" t="n">
+        <v>-1436</v>
+      </c>
+      <c r="M187" s="12" t="n">
+        <v>-693</v>
+      </c>
+      <c r="O187" s="12" t="n">
+        <v>-1697.518</v>
+      </c>
+      <c r="P187" s="12" t="n">
+        <v>-3557.564</v>
+      </c>
+      <c r="Q187" s="12" t="n">
+        <v>-1762.062</v>
+      </c>
+      <c r="R187" s="12" t="n">
+        <v>-1837.24</v>
+      </c>
+      <c r="S187" s="12" t="n">
+        <v>-351.051</v>
+      </c>
+      <c r="T187" s="12" t="n">
+        <v>-1818.386</v>
+      </c>
+      <c r="U187" s="12" t="n">
+        <v>-1440.824</v>
+      </c>
+      <c r="V187" s="12" t="n">
+        <v>-1087.958</v>
+      </c>
+      <c r="W187" s="12" t="n">
+        <v>-1391</v>
+      </c>
+      <c r="X187" s="12" t="n">
+        <v>-1436</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C188" s="12" t="n">
-        <v>-626.537</v>
-      </c>
-      <c r="E188" s="12" t="n">
-        <v>-285</v>
-      </c>
-      <c r="G188" s="12" t="n">
-        <v>-564</v>
-      </c>
-      <c r="I188" s="12" t="n">
-        <v>-196</v>
-      </c>
-      <c r="K188" s="12" t="n">
-        <v>-403</v>
-      </c>
-      <c r="M188" s="12" t="n">
-        <v>-237</v>
-      </c>
-      <c r="O188" s="12" t="n">
-        <v>-314.185</v>
-      </c>
-      <c r="P188" s="12" t="n">
-        <v>-357.102</v>
-      </c>
-      <c r="Q188" s="12" t="n">
-        <v>-381.223</v>
-      </c>
-      <c r="R188" s="12" t="n">
-        <v>-371.046</v>
-      </c>
-      <c r="S188" s="12" t="n">
-        <v>4758.174</v>
-      </c>
-      <c r="T188" s="12" t="n">
-        <v>520.23</v>
-      </c>
-      <c r="U188" s="12" t="n">
-        <v>-6116.776</v>
-      </c>
-      <c r="V188" s="12" t="n">
-        <v>-626.537</v>
-      </c>
-      <c r="W188" s="12" t="n">
-        <v>-564</v>
-      </c>
-      <c r="X188" s="12" t="n">
-        <v>-403</v>
+      <c r="A188" s="20" t="inlineStr">
+        <is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="C188" s="22" t="n">
+        <v>-18.336</v>
+      </c>
+      <c r="E188" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G188" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" s="22" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="P188" s="22" t="n">
+        <v>2.068</v>
+      </c>
+      <c r="Q188" s="22" t="n">
+        <v>-4.884</v>
+      </c>
+      <c r="R188" s="22" t="n">
+        <v>6.984</v>
+      </c>
+      <c r="S188" s="22" t="n">
+        <v>-43.2</v>
+      </c>
+      <c r="T188" s="22" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="U188" s="22" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="V188" s="22" t="n">
+        <v>-18.336</v>
+      </c>
+      <c r="W188" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X188" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 증감</t>
-        </is>
-      </c>
-      <c r="C189" s="22" t="n">
-        <v>831.27</v>
-      </c>
-      <c r="E189" s="22" t="n">
-        <v>329</v>
-      </c>
-      <c r="G189" s="22" t="n">
-        <v>712</v>
-      </c>
-      <c r="I189" s="22" t="n">
-        <v>887</v>
-      </c>
-      <c r="K189" s="22" t="n">
-        <v>1526</v>
-      </c>
-      <c r="M189" s="22" t="n">
-        <v>1490</v>
-      </c>
-      <c r="O189" s="22" t="n">
-        <v>757.9349999999999</v>
-      </c>
-      <c r="P189" s="22" t="n">
-        <v>-1381.579</v>
-      </c>
-      <c r="Q189" s="22" t="n">
-        <v>649.71</v>
+          <t>장기차입</t>
+        </is>
       </c>
       <c r="R189" s="22" t="n">
-        <v>211.89</v>
+        <v>0</v>
       </c>
       <c r="S189" s="22" t="n">
-        <v>4349.21</v>
+        <v>5000</v>
       </c>
       <c r="T189" s="22" t="n">
-        <v>1123.428</v>
+        <v>1000</v>
       </c>
       <c r="U189" s="22" t="n">
-        <v>-5936.381</v>
-      </c>
-      <c r="V189" s="22" t="n">
-        <v>831.27</v>
-      </c>
-      <c r="W189" s="22" t="n">
-        <v>712</v>
-      </c>
-      <c r="X189" s="22" t="n">
-        <v>1526</v>
+        <v>700</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="20" t="inlineStr">
         <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="C190" s="22" t="n">
+        <v>-348</v>
+      </c>
+      <c r="E190" s="22" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G190" s="22" t="n">
+        <v>-202</v>
+      </c>
+      <c r="I190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" s="22" t="n">
+        <v>-199.992</v>
+      </c>
+      <c r="U190" s="22" t="n">
+        <v>-6032.008</v>
+      </c>
+      <c r="V190" s="22" t="n">
+        <v>-348</v>
+      </c>
+      <c r="W190" s="22" t="n">
+        <v>-202</v>
+      </c>
+      <c r="X190" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="C191" s="22" t="n">
+        <v>-20.132</v>
+      </c>
+      <c r="E191" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K191" s="22" t="n">
+        <v>-29</v>
+      </c>
+      <c r="M191" s="22" t="n">
+        <v>-14</v>
+      </c>
+      <c r="O191" s="22" t="n">
+        <v>-12.162</v>
+      </c>
+      <c r="P191" s="22" t="n">
+        <v>-12.662</v>
+      </c>
+      <c r="Q191" s="22" t="n">
+        <v>-14.228</v>
+      </c>
+      <c r="R191" s="22" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="S191" s="22" t="n">
+        <v>-16.95</v>
+      </c>
+      <c r="T191" s="22" t="n">
+        <v>-18.75</v>
+      </c>
+      <c r="U191" s="22" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>-20.132</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>-25</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C192" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I192" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K192" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M192" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O192" s="22" t="n">
+        <v>-0.249</v>
+      </c>
+      <c r="P192" s="22" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="Q192" s="22" t="n">
+        <v>-0.392</v>
+      </c>
+      <c r="R192" s="22" t="n">
+        <v>-0.163</v>
+      </c>
+      <c r="S192" s="22" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="T192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" s="22" t="n">
+        <v>-524.232</v>
+      </c>
+      <c r="V192" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="W192" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X192" s="22" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C193" s="22" t="n">
+        <v>-239.989</v>
+      </c>
+      <c r="E193" s="22" t="n">
+        <v>-146</v>
+      </c>
+      <c r="G193" s="22" t="n">
+        <v>-324</v>
+      </c>
+      <c r="I193" s="22" t="n">
+        <v>-180</v>
+      </c>
+      <c r="K193" s="22" t="n">
+        <v>-373</v>
+      </c>
+      <c r="M193" s="22" t="n">
+        <v>-223</v>
+      </c>
+      <c r="O193" s="22" t="n">
+        <v>-301.233</v>
+      </c>
+      <c r="P193" s="22" t="n">
+        <v>-346.273</v>
+      </c>
+      <c r="Q193" s="22" t="n">
+        <v>-361.718</v>
+      </c>
+      <c r="R193" s="22" t="n">
+        <v>-362.274</v>
+      </c>
+      <c r="S193" s="22" t="n">
+        <v>-181.482</v>
+      </c>
+      <c r="T193" s="22" t="n">
+        <v>-241.427</v>
+      </c>
+      <c r="U193" s="22" t="n">
+        <v>-269.994</v>
+      </c>
+      <c r="V193" s="22" t="n">
+        <v>-239.989</v>
+      </c>
+      <c r="W193" s="22" t="n">
+        <v>-324</v>
+      </c>
+      <c r="X193" s="22" t="n">
+        <v>-373</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" s="22" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="X194" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="n">
+        <v>-626.537</v>
+      </c>
+      <c r="E195" s="12" t="n">
+        <v>-285</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>-564</v>
+      </c>
+      <c r="I195" s="12" t="n">
+        <v>-196</v>
+      </c>
+      <c r="K195" s="12" t="n">
+        <v>-403</v>
+      </c>
+      <c r="M195" s="12" t="n">
+        <v>-237</v>
+      </c>
+      <c r="O195" s="12" t="n">
+        <v>-314.185</v>
+      </c>
+      <c r="P195" s="12" t="n">
+        <v>-357.102</v>
+      </c>
+      <c r="Q195" s="12" t="n">
+        <v>-381.223</v>
+      </c>
+      <c r="R195" s="12" t="n">
+        <v>-371.046</v>
+      </c>
+      <c r="S195" s="12" t="n">
+        <v>4758.174</v>
+      </c>
+      <c r="T195" s="12" t="n">
+        <v>520.23</v>
+      </c>
+      <c r="U195" s="12" t="n">
+        <v>-6116.776</v>
+      </c>
+      <c r="V195" s="12" t="n">
+        <v>-626.537</v>
+      </c>
+      <c r="W195" s="12" t="n">
+        <v>-564</v>
+      </c>
+      <c r="X195" s="12" t="n">
+        <v>-403</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 증감</t>
+        </is>
+      </c>
+      <c r="C196" s="22" t="n">
+        <v>831.27</v>
+      </c>
+      <c r="E196" s="22" t="n">
+        <v>329</v>
+      </c>
+      <c r="G196" s="22" t="n">
+        <v>712</v>
+      </c>
+      <c r="I196" s="22" t="n">
+        <v>887</v>
+      </c>
+      <c r="K196" s="22" t="n">
+        <v>1526</v>
+      </c>
+      <c r="M196" s="22" t="n">
+        <v>1490</v>
+      </c>
+      <c r="O196" s="22" t="n">
+        <v>757.9349999999999</v>
+      </c>
+      <c r="P196" s="22" t="n">
+        <v>-1381.579</v>
+      </c>
+      <c r="Q196" s="22" t="n">
+        <v>649.71</v>
+      </c>
+      <c r="R196" s="22" t="n">
+        <v>211.89</v>
+      </c>
+      <c r="S196" s="22" t="n">
+        <v>4349.21</v>
+      </c>
+      <c r="T196" s="22" t="n">
+        <v>1123.428</v>
+      </c>
+      <c r="U196" s="22" t="n">
+        <v>-5936.381</v>
+      </c>
+      <c r="V196" s="22" t="n">
+        <v>831.27</v>
+      </c>
+      <c r="W196" s="22" t="n">
+        <v>712</v>
+      </c>
+      <c r="X196" s="22" t="n">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="20" t="inlineStr">
+        <is>
           <t>신규 연결 현금성자산 증가</t>
         </is>
       </c>
-      <c r="C190" s="22" t="n">
+      <c r="C197" s="22" t="n">
         <v>134.804</v>
       </c>
-      <c r="E190" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V190" s="22" t="n">
+      <c r="E197" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" s="22" t="n">
         <v>134.804</v>
       </c>
-      <c r="W190" s="22" t="n">
+      <c r="W197" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10595,7 +11006,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -12033,7 +12444,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -12085,7 +12496,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -12137,7 +12548,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -12189,7 +12600,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -12241,7 +12652,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12293,7 +12704,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12345,7 +12756,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12355,43 +12766,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -12415,7 +12826,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12467,7 +12878,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12519,7 +12930,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12571,7 +12982,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12623,7 +13034,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12675,7 +13086,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12745,7 +13156,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12797,7 +13208,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12807,49 +13218,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12859,49 +13270,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12911,49 +13322,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12963,43 +13374,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -13023,7 +13434,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -13075,7 +13486,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -13127,7 +13538,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -13179,7 +13590,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15840,642 +16251,642 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>브롱코빌리 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>ttm 순이익</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>2023-Q4</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>10.03</v>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>2024-Q1</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>13.42</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>2024-Q2</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>14.92</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>2024-Q3</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="57" t="n">
         <v>16.35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>2024-Q4</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="57" t="n">
         <v>17.15</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>2025-Q1</t>
         </is>
       </c>
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="57" t="n">
         <v>15.61</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>2025-Q2</t>
         </is>
       </c>
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="57" t="n">
         <v>17.33</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>2025-Q3</t>
         </is>
       </c>
-      <c r="B13" s="56" t="n">
+      <c r="B13" s="57" t="n">
         <v>17.65</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="57" t="n">
         <v>19.69</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="B15" s="56" t="n">
+      <c r="B15" s="57" t="n">
         <v>22.89</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="57" t="n">
         <v>24.17</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="55" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>2026-Q3</t>
         </is>
       </c>
-      <c r="B17" s="56" t="n">
+      <c r="B17" s="57" t="n">
         <v>25.99</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="54" t="inlineStr">
         <is>
           <t>EPS ttm</t>
         </is>
       </c>
-      <c r="B19" s="53" t="n"/>
-      <c r="C19" s="53" t="n"/>
+      <c r="B19" s="54" t="n"/>
+      <c r="C19" s="54" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B20" s="54" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C20" s="54" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>2023-Q4</t>
         </is>
       </c>
-      <c r="B21" s="56" t="n">
+      <c r="B21" s="57" t="n">
         <v>33.67</v>
       </c>
-      <c r="C21" s="57" t="inlineStr">
+      <c r="C21" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>2024-Q1</t>
         </is>
       </c>
-      <c r="B22" s="56" t="n">
+      <c r="B22" s="57" t="n">
         <v>45.05</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="56" t="inlineStr">
         <is>
           <t>2024-Q2</t>
         </is>
       </c>
-      <c r="B23" s="56" t="n">
+      <c r="B23" s="57" t="n">
         <v>50.09</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>2024-Q3</t>
         </is>
       </c>
-      <c r="B24" s="56" t="n">
+      <c r="B24" s="57" t="n">
         <v>54.89</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>2024-Q4</t>
         </is>
       </c>
-      <c r="B25" s="56" t="n">
+      <c r="B25" s="57" t="n">
         <v>57.57</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>2025-Q1</t>
         </is>
       </c>
-      <c r="B26" s="56" t="n">
+      <c r="B26" s="57" t="n">
         <v>52.4</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>2025-Q2</t>
         </is>
       </c>
-      <c r="B27" s="56" t="n">
+      <c r="B27" s="57" t="n">
         <v>58.18</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>2025-Q3</t>
         </is>
       </c>
-      <c r="B28" s="56" t="n">
+      <c r="B28" s="57" t="n">
         <v>59.25</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="B29" s="56" t="n">
+      <c r="B29" s="57" t="n">
         <v>66.09999999999999</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="55" t="inlineStr">
+      <c r="A30" s="56" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="B30" s="56" t="n">
+      <c r="B30" s="57" t="n">
         <v>76.84</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="B31" s="56" t="n">
+      <c r="B31" s="57" t="n">
         <v>81.14</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>2026-Q3</t>
         </is>
       </c>
-      <c r="B32" s="56" t="n">
+      <c r="B32" s="57" t="n">
         <v>87.25</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="A34" s="54" t="inlineStr">
         <is>
           <t>inc 이익률</t>
         </is>
       </c>
-      <c r="B34" s="53" t="n"/>
-      <c r="C34" s="53" t="n"/>
+      <c r="B34" s="54" t="n"/>
+      <c r="C34" s="54" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="54" t="inlineStr">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B35" s="54" t="inlineStr">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C35" s="54" t="inlineStr">
+      <c r="C35" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="55" t="inlineStr">
+      <c r="A36" s="56" t="inlineStr">
         <is>
           <t>2024-Q2</t>
         </is>
       </c>
-      <c r="B36" s="56" t="n">
+      <c r="B36" s="57" t="n">
         <v>41.1</v>
       </c>
-      <c r="C36" s="57" t="inlineStr">
+      <c r="C36" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="55" t="inlineStr">
+      <c r="A37" s="56" t="inlineStr">
         <is>
           <t>2024-Q3</t>
         </is>
       </c>
-      <c r="B37" s="56" t="n">
+      <c r="B37" s="57" t="n">
         <v>15.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>2024-Q4</t>
         </is>
       </c>
-      <c r="B38" s="56" t="n">
+      <c r="B38" s="57" t="n">
         <v>7.6</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>2025-Q1</t>
         </is>
       </c>
-      <c r="B39" s="56" t="n">
+      <c r="B39" s="57" t="n">
         <v>-32.4</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>2025-Q2</t>
         </is>
       </c>
-      <c r="B40" s="56" t="n">
+      <c r="B40" s="57" t="n">
         <v>21.6</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>2025-Q3</t>
         </is>
       </c>
-      <c r="B41" s="56" t="n">
+      <c r="B41" s="57" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="B42" s="56" t="n">
+      <c r="B42" s="57" t="n">
         <v>32.8</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="55" t="inlineStr">
+      <c r="A43" s="56" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="B43" s="56" t="n">
+      <c r="B43" s="57" t="n">
         <v>52.1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="55" t="inlineStr">
+      <c r="A44" s="56" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="B44" s="56" t="n">
+      <c r="B44" s="57" t="n">
         <v>22.2</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="55" t="inlineStr">
+      <c r="A45" s="56" t="inlineStr">
         <is>
           <t>2026-Q3</t>
         </is>
       </c>
-      <c r="B45" s="56" t="n">
+      <c r="B45" s="57" t="n">
         <v>29.2</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="inlineStr">
+      <c r="A47" s="54" t="inlineStr">
         <is>
           <t>가이던스 fy26 · initial 0120</t>
         </is>
       </c>
-      <c r="B47" s="53" t="n"/>
-      <c r="C47" s="53" t="n"/>
+      <c r="B47" s="54" t="n"/>
+      <c r="C47" s="54" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B48" s="54" t="inlineStr">
+      <c r="B48" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C48" s="54" t="inlineStr">
+      <c r="C48" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B49" s="58" t="n">
+      <c r="B49" s="59" t="n">
         <v>330</v>
       </c>
-      <c r="C49" s="57" t="inlineStr">
+      <c r="C49" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="55" t="inlineStr">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B50" s="56" t="n">
+      <c r="B50" s="57" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="55" t="inlineStr">
+      <c r="A51" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B51" s="56" t="n">
+      <c r="B51" s="57" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="53" t="inlineStr">
+      <c r="A53" s="54" t="inlineStr">
         <is>
           <t>가이던스 fy26 · 매출 0722</t>
         </is>
       </c>
-      <c r="B53" s="53" t="n"/>
-      <c r="C53" s="53" t="n"/>
+      <c r="B53" s="54" t="n"/>
+      <c r="C53" s="54" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="54" t="inlineStr">
+      <c r="A54" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B54" s="54" t="inlineStr">
+      <c r="B54" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C54" s="54" t="inlineStr">
+      <c r="C54" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="55" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B55" s="58" t="n">
+      <c r="B55" s="59" t="n">
         <v>340</v>
       </c>
-      <c r="C55" s="57" t="inlineStr">
+      <c r="C55" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="55" t="inlineStr">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B56" s="56" t="n">
+      <c r="B56" s="57" t="n">
         <v>39.7</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B57" s="56" t="n">
+      <c r="B57" s="57" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="54" t="inlineStr">
         <is>
           <t>sss 2026</t>
         </is>
       </c>
-      <c r="B59" s="53" t="n"/>
-      <c r="C59" s="53" t="n"/>
+      <c r="B59" s="54" t="n"/>
+      <c r="C59" s="54" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="54" t="inlineStr">
+      <c r="A60" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B60" s="54" t="inlineStr">
+      <c r="B60" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C60" s="54" t="inlineStr">
+      <c r="C60" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="55" t="inlineStr">
+      <c r="A61" s="56" t="inlineStr">
         <is>
           <t>1Q</t>
         </is>
       </c>
-      <c r="B61" s="56" t="n">
+      <c r="B61" s="57" t="n">
         <v>106.7</v>
       </c>
-      <c r="C61" s="57" t="inlineStr">
+      <c r="C61" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>2Q</t>
         </is>
       </c>
-      <c r="B62" s="56" t="n">
+      <c r="B62" s="57" t="n">
         <v>108.8</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="inlineStr">
+      <c r="A63" s="56" t="inlineStr">
         <is>
           <t>3Q</t>
         </is>
       </c>
-      <c r="B63" s="56" t="n">
+      <c r="B63" s="57" t="n">
         <v>107.9</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="55" t="inlineStr">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B64" s="56" t="n">
+      <c r="B64" s="57" t="n">
         <v>107.8</v>
       </c>
     </row>
@@ -16499,24 +16910,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/docs/data/jp/xlsx/3091.xlsx
+++ b/docs/data/jp/xlsx/3091.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -381,6 +381,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4958,11 +4961,11 @@
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.28)</t>
+          <t>현재 주가 (2026.10.29)</t>
         </is>
       </c>
       <c r="B53" s="29" t="n">
-        <v>3095</v>
+        <v>2998</v>
       </c>
       <c r="C53" s="30" t="n"/>
       <c r="D53" s="31" t="n"/>
@@ -6199,7 +6202,7 @@
     <row r="80">
       <c r="A80" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.28</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.29</t>
         </is>
       </c>
       <c r="C80" s="41" t="n"/>
@@ -17268,12 +17271,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:Z105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="44" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17293,11 +17319,34 @@
     <row r="4">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>ttm 순이익</t>
+          <t>월차</t>
         </is>
       </c>
       <c r="B4" s="54" t="n"/>
       <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="54" t="n"/>
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="54" t="n"/>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="55" t="inlineStr">
@@ -17307,10 +17356,125 @@
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="K5" s="55" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L5" s="55" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="M5" s="55" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="O5" s="55" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="P5" s="55" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="Q5" s="55" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="R5" s="55" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="S5" s="55" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="T5" s="55" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="U5" s="55" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="V5" s="55" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="W5" s="55" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="X5" s="55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="Y5" s="55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="Z5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
@@ -17319,601 +17483,1518 @@
     <row r="6">
       <c r="A6" s="56" t="inlineStr">
         <is>
-          <t>2023-Q4</t>
+          <t>기존점 매출 전년 대비</t>
         </is>
       </c>
       <c r="B6" s="57" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="C6" s="58" t="inlineStr">
-        <is>
-          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        <v>109.8</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="G6" s="57" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I6" s="57" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="J6" s="57" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="K6" s="57" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="L6" s="57" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="M6" s="57" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="N6" s="57" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="O6" s="57" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="P6" s="57" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="Q6" s="57" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="R6" s="57" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="S6" s="57" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="T6" s="57" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="U6" s="57" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="V6" s="57" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="W6" s="57" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="X6" s="57" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y6" s="58" t="n"/>
+      <c r="Z6" s="59" t="inlineStr">
+        <is>
+          <t>https://www.release.tdnet.info/inbs/140120261022554350.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="56" t="inlineStr">
         <is>
-          <t>2024-Q1</t>
+          <t>기존점 객수 전년 대비</t>
         </is>
       </c>
       <c r="B7" s="57" t="n">
-        <v>13.42</v>
-      </c>
+        <v>104.9</v>
+      </c>
+      <c r="C7" s="57" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G7" s="57" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="I7" s="57" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="L7" s="57" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M7" s="57" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N7" s="57" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="O7" s="57" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="P7" s="57" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="Q7" s="57" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="R7" s="57" t="n">
+        <v>104</v>
+      </c>
+      <c r="S7" s="57" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="T7" s="57" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U7" s="57" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="V7" s="57" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="W7" s="57" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="X7" s="57" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="Y7" s="58" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="56" t="inlineStr">
         <is>
-          <t>2024-Q2</t>
+          <t>기존점 객단가 전년 대비</t>
         </is>
       </c>
       <c r="B8" s="57" t="n">
-        <v>14.92</v>
-      </c>
+        <v>104.7</v>
+      </c>
+      <c r="C8" s="57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="F8" s="57" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="G8" s="57" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="H8" s="57" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="I8" s="57" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="J8" s="57" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="K8" s="57" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="L8" s="57" t="n">
+        <v>106</v>
+      </c>
+      <c r="M8" s="57" t="n">
+        <v>101</v>
+      </c>
+      <c r="N8" s="57" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="O8" s="57" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="P8" s="57" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="Q8" s="57" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="R8" s="57" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="S8" s="57" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="T8" s="57" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="U8" s="57" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="V8" s="57" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="W8" s="57" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="X8" s="57" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="Y8" s="58" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="56" t="inlineStr">
         <is>
-          <t>2024-Q3</t>
-        </is>
-      </c>
-      <c r="B9" s="57" t="n">
-        <v>16.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="56" t="inlineStr">
-        <is>
-          <t>2024-Q4</t>
-        </is>
-      </c>
-      <c r="B10" s="57" t="n">
-        <v>17.15</v>
+          <t>기존점 매출 전년 대비(분기 평균)</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="n"/>
+      <c r="C9" s="58" t="n"/>
+      <c r="D9" s="58" t="n"/>
+      <c r="E9" s="58" t="n"/>
+      <c r="F9" s="58" t="n"/>
+      <c r="G9" s="58" t="n"/>
+      <c r="H9" s="58" t="n"/>
+      <c r="I9" s="58" t="n"/>
+      <c r="J9" s="58" t="n"/>
+      <c r="K9" s="58" t="n"/>
+      <c r="L9" s="58" t="n"/>
+      <c r="M9" s="58" t="n"/>
+      <c r="N9" s="58" t="n"/>
+      <c r="O9" s="58" t="n"/>
+      <c r="P9" s="58" t="n"/>
+      <c r="Q9" s="58" t="n"/>
+      <c r="R9" s="58" t="n"/>
+      <c r="S9" s="58" t="n"/>
+      <c r="T9" s="58" t="n"/>
+      <c r="U9" s="58" t="n"/>
+      <c r="V9" s="58" t="n"/>
+      <c r="W9" s="58" t="n"/>
+      <c r="X9" s="58" t="n"/>
+      <c r="Y9" s="57" t="n">
+        <v>107.9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="56" t="inlineStr">
-        <is>
-          <t>2025-Q1</t>
-        </is>
-      </c>
-      <c r="B11" s="57" t="n">
-        <v>15.61</v>
-      </c>
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>this results · 3Q single</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="n"/>
+      <c r="C11" s="54" t="n"/>
+      <c r="D11" s="54" t="n"/>
+      <c r="E11" s="54" t="n"/>
+      <c r="F11" s="54" t="n"/>
+      <c r="G11" s="54" t="n"/>
+      <c r="H11" s="54" t="n"/>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="54" t="n"/>
+      <c r="L11" s="54" t="n"/>
+      <c r="M11" s="54" t="n"/>
+      <c r="N11" s="54" t="n"/>
+      <c r="O11" s="54" t="n"/>
+      <c r="P11" s="54" t="n"/>
+      <c r="Q11" s="54" t="n"/>
+      <c r="R11" s="54" t="n"/>
+      <c r="S11" s="54" t="n"/>
+      <c r="T11" s="54" t="n"/>
+      <c r="U11" s="54" t="n"/>
+      <c r="V11" s="54" t="n"/>
+      <c r="W11" s="54" t="n"/>
+      <c r="X11" s="54" t="n"/>
+      <c r="Y11" s="54" t="n"/>
+      <c r="Z11" s="54" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="56" t="inlineStr">
-        <is>
-          <t>2025-Q2</t>
-        </is>
-      </c>
-      <c r="B12" s="57" t="n">
-        <v>17.33</v>
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z12" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="56" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>매출</t>
         </is>
       </c>
       <c r="B13" s="57" t="n">
-        <v>17.65</v>
+        <v>88.77</v>
+      </c>
+      <c r="Z13" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="56" t="inlineStr">
         <is>
-          <t>2025-Q4</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="B14" s="57" t="n">
-        <v>19.69</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="56" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>gp</t>
         </is>
       </c>
       <c r="B15" s="57" t="n">
-        <v>22.89</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="56" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>sga</t>
         </is>
       </c>
       <c r="B16" s="57" t="n">
-        <v>24.17</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="56" t="inlineStr">
         <is>
-          <t>2026-Q3</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="B17" s="57" t="n">
-        <v>25.99</v>
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="n">
+        <v>11.32</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="inlineStr">
-        <is>
-          <t>EPS ttm</t>
-        </is>
-      </c>
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="54" t="n"/>
+      <c r="A19" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="n">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B20" s="55" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C20" s="55" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>매출 YoY</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="n">
+        <v>12.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="56" t="inlineStr">
         <is>
-          <t>2023-Q4</t>
+          <t>gp YoY</t>
         </is>
       </c>
       <c r="B21" s="57" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="C21" s="58" t="inlineStr">
-        <is>
-          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
-        </is>
+        <v>11.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="56" t="inlineStr">
         <is>
-          <t>2024-Q1</t>
+          <t>sga YoY</t>
         </is>
       </c>
       <c r="B22" s="57" t="n">
-        <v>45.05</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="56" t="inlineStr">
         <is>
-          <t>2024-Q2</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="B23" s="57" t="n">
-        <v>50.09</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="56" t="inlineStr">
         <is>
-          <t>2024-Q3</t>
+          <t>ord YoY</t>
         </is>
       </c>
       <c r="B24" s="57" t="n">
-        <v>54.89</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="56" t="inlineStr">
         <is>
-          <t>2024-Q4</t>
+          <t>순이익 YoY</t>
         </is>
       </c>
       <c r="B25" s="57" t="n">
-        <v>57.57</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="56" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>매출총이익률</t>
         </is>
       </c>
       <c r="B26" s="57" t="n">
-        <v>52.4</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="56" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>매출총이익률 ly</t>
         </is>
       </c>
       <c r="B27" s="57" t="n">
-        <v>58.18</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="56" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>sga ratio</t>
         </is>
       </c>
       <c r="B28" s="57" t="n">
-        <v>59.25</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="56" t="inlineStr">
         <is>
-          <t>2025-Q4</t>
+          <t>sga ratio ly</t>
         </is>
       </c>
       <c r="B29" s="57" t="n">
-        <v>66.09999999999999</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="56" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>영업이익률</t>
         </is>
       </c>
       <c r="B30" s="57" t="n">
-        <v>76.84</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="56" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>영업이익률 ly</t>
         </is>
       </c>
       <c r="B31" s="57" t="n">
-        <v>81.14</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="56" t="inlineStr">
-        <is>
-          <t>2026-Q3</t>
-        </is>
-      </c>
-      <c r="B32" s="57" t="n">
-        <v>87.25</v>
-      </c>
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="54" t="inlineStr">
+        <is>
+          <t>this results · ytd9m</t>
+        </is>
+      </c>
+      <c r="B33" s="54" t="n"/>
+      <c r="C33" s="54" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="54" t="n"/>
+      <c r="F33" s="54" t="n"/>
+      <c r="G33" s="54" t="n"/>
+      <c r="H33" s="54" t="n"/>
+      <c r="I33" s="54" t="n"/>
+      <c r="J33" s="54" t="n"/>
+      <c r="K33" s="54" t="n"/>
+      <c r="L33" s="54" t="n"/>
+      <c r="M33" s="54" t="n"/>
+      <c r="N33" s="54" t="n"/>
+      <c r="O33" s="54" t="n"/>
+      <c r="P33" s="54" t="n"/>
+      <c r="Q33" s="54" t="n"/>
+      <c r="R33" s="54" t="n"/>
+      <c r="S33" s="54" t="n"/>
+      <c r="T33" s="54" t="n"/>
+      <c r="U33" s="54" t="n"/>
+      <c r="V33" s="54" t="n"/>
+      <c r="W33" s="54" t="n"/>
+      <c r="X33" s="54" t="n"/>
+      <c r="Y33" s="54" t="n"/>
+      <c r="Z33" s="54" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="inlineStr">
-        <is>
-          <t>inc 이익률</t>
-        </is>
-      </c>
-      <c r="B34" s="54" t="n"/>
-      <c r="C34" s="54" t="n"/>
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z34" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="55" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B35" s="55" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C35" s="55" t="inlineStr">
-        <is>
-          <t>출처</t>
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B35" s="57" t="n">
+        <v>253.51</v>
+      </c>
+      <c r="Z35" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="56" t="inlineStr">
         <is>
-          <t>2024-Q2</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="B36" s="57" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="C36" s="58" t="inlineStr">
-        <is>
-          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
-        </is>
+        <v>30.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="56" t="inlineStr">
         <is>
-          <t>2024-Q3</t>
+          <t>ord</t>
         </is>
       </c>
       <c r="B37" s="57" t="n">
-        <v>15.4</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="56" t="inlineStr">
         <is>
-          <t>2024-Q4</t>
+          <t>순이익</t>
         </is>
       </c>
       <c r="B38" s="57" t="n">
-        <v>7.6</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="56" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>매출 YoY</t>
         </is>
       </c>
       <c r="B39" s="57" t="n">
-        <v>-32.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="56" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="B40" s="57" t="n">
-        <v>21.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="56" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>순이익 YoY</t>
         </is>
       </c>
       <c r="B41" s="57" t="n">
-        <v>6.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="56" t="inlineStr">
         <is>
-          <t>2025-Q4</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B42" s="57" t="n">
-        <v>32.8</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="56" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>cogs ratio</t>
         </is>
       </c>
       <c r="B43" s="57" t="n">
-        <v>52.1</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="56" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>영업이익률</t>
         </is>
       </c>
       <c r="B44" s="57" t="n">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="56" t="inlineStr">
-        <is>
-          <t>2026-Q3</t>
-        </is>
-      </c>
-      <c r="B45" s="57" t="n">
-        <v>29.2</v>
-      </c>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>this results · gross 매출 3Q</t>
+        </is>
+      </c>
+      <c r="B46" s="54" t="n"/>
+      <c r="C46" s="54" t="n"/>
+      <c r="D46" s="54" t="n"/>
+      <c r="E46" s="54" t="n"/>
+      <c r="F46" s="54" t="n"/>
+      <c r="G46" s="54" t="n"/>
+      <c r="H46" s="54" t="n"/>
+      <c r="I46" s="54" t="n"/>
+      <c r="J46" s="54" t="n"/>
+      <c r="K46" s="54" t="n"/>
+      <c r="L46" s="54" t="n"/>
+      <c r="M46" s="54" t="n"/>
+      <c r="N46" s="54" t="n"/>
+      <c r="O46" s="54" t="n"/>
+      <c r="P46" s="54" t="n"/>
+      <c r="Q46" s="54" t="n"/>
+      <c r="R46" s="54" t="n"/>
+      <c r="S46" s="54" t="n"/>
+      <c r="T46" s="54" t="n"/>
+      <c r="U46" s="54" t="n"/>
+      <c r="V46" s="54" t="n"/>
+      <c r="W46" s="54" t="n"/>
+      <c r="X46" s="54" t="n"/>
+      <c r="Y46" s="54" t="n"/>
+      <c r="Z46" s="54" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="54" t="inlineStr">
-        <is>
-          <t>가이던스 fy26 · initial 0120</t>
-        </is>
-      </c>
-      <c r="B47" s="54" t="n"/>
-      <c r="C47" s="54" t="n"/>
+      <c r="A47" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B47" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z47" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="55" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B48" s="55" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C48" s="55" t="inlineStr">
-        <is>
-          <t>출처</t>
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="B48" s="57" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="Z48" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="56" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B49" s="59" t="n">
-        <v>330</v>
-      </c>
-      <c r="C49" s="58" t="inlineStr">
-        <is>
-          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
-        </is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="B49" s="57" t="n">
+        <v>-7.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="56" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>discount rate</t>
         </is>
       </c>
       <c r="B50" s="57" t="n">
-        <v>30</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="56" t="inlineStr">
         <is>
-          <t>순이익</t>
+          <t>gross ly</t>
         </is>
       </c>
       <c r="B51" s="57" t="n">
-        <v>20</v>
+        <v>85.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>discount ly</t>
+        </is>
+      </c>
+      <c r="B52" s="57" t="n">
+        <v>-6.46</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="54" t="inlineStr">
-        <is>
-          <t>가이던스 fy26 · 매출 0722</t>
-        </is>
-      </c>
-      <c r="B53" s="54" t="n"/>
-      <c r="C53" s="54" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="55" t="inlineStr">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>rate ly</t>
+        </is>
+      </c>
+      <c r="B53" s="57" t="n">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="54" t="inlineStr">
+        <is>
+          <t>this results · 기존점 점포 매출 YoY 2026</t>
+        </is>
+      </c>
+      <c r="B55" s="54" t="n"/>
+      <c r="C55" s="54" t="n"/>
+      <c r="D55" s="54" t="n"/>
+      <c r="E55" s="54" t="n"/>
+      <c r="F55" s="54" t="n"/>
+      <c r="G55" s="54" t="n"/>
+      <c r="H55" s="54" t="n"/>
+      <c r="I55" s="54" t="n"/>
+      <c r="J55" s="54" t="n"/>
+      <c r="K55" s="54" t="n"/>
+      <c r="L55" s="54" t="n"/>
+      <c r="M55" s="54" t="n"/>
+      <c r="N55" s="54" t="n"/>
+      <c r="O55" s="54" t="n"/>
+      <c r="P55" s="54" t="n"/>
+      <c r="Q55" s="54" t="n"/>
+      <c r="R55" s="54" t="n"/>
+      <c r="S55" s="54" t="n"/>
+      <c r="T55" s="54" t="n"/>
+      <c r="U55" s="54" t="n"/>
+      <c r="V55" s="54" t="n"/>
+      <c r="W55" s="54" t="n"/>
+      <c r="X55" s="54" t="n"/>
+      <c r="Y55" s="54" t="n"/>
+      <c r="Z55" s="54" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B54" s="55" t="inlineStr">
+      <c r="B56" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C54" s="55" t="inlineStr">
+      <c r="Z56" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="56" t="inlineStr">
-        <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B55" s="59" t="n">
-        <v>340</v>
-      </c>
-      <c r="C55" s="58" t="inlineStr">
-        <is>
-          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="56" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="B56" s="57" t="n">
-        <v>39.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="56" t="inlineStr">
         <is>
-          <t>순이익</t>
+          <t>1Q</t>
         </is>
       </c>
       <c r="B57" s="57" t="n">
-        <v>26</v>
+        <v>106.7</v>
+      </c>
+      <c r="Z57" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
+        <is>
+          <t>2Q</t>
+        </is>
+      </c>
+      <c r="B58" s="57" t="n">
+        <v>108.8</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="54" t="inlineStr">
-        <is>
-          <t>sss 2026</t>
-        </is>
-      </c>
-      <c r="B59" s="54" t="n"/>
-      <c r="C59" s="54" t="n"/>
+      <c r="A59" s="56" t="inlineStr">
+        <is>
+          <t>3Q</t>
+        </is>
+      </c>
+      <c r="B59" s="57" t="n">
+        <v>107.9</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="55" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B60" s="55" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C60" s="55" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>1~9월</t>
+        </is>
+      </c>
+      <c r="B60" s="57" t="n">
+        <v>107.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="56" t="inlineStr">
         <is>
-          <t>1Q</t>
+          <t>상반기</t>
         </is>
       </c>
       <c r="B61" s="57" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="C61" s="58" t="inlineStr">
+        <v>107.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="54" t="inlineStr">
+        <is>
+          <t>this results · 점포</t>
+        </is>
+      </c>
+      <c r="B63" s="54" t="n"/>
+      <c r="C63" s="54" t="n"/>
+      <c r="D63" s="54" t="n"/>
+      <c r="E63" s="54" t="n"/>
+      <c r="F63" s="54" t="n"/>
+      <c r="G63" s="54" t="n"/>
+      <c r="H63" s="54" t="n"/>
+      <c r="I63" s="54" t="n"/>
+      <c r="J63" s="54" t="n"/>
+      <c r="K63" s="54" t="n"/>
+      <c r="L63" s="54" t="n"/>
+      <c r="M63" s="54" t="n"/>
+      <c r="N63" s="54" t="n"/>
+      <c r="O63" s="54" t="n"/>
+      <c r="P63" s="54" t="n"/>
+      <c r="Q63" s="54" t="n"/>
+      <c r="R63" s="54" t="n"/>
+      <c r="S63" s="54" t="n"/>
+      <c r="T63" s="54" t="n"/>
+      <c r="U63" s="54" t="n"/>
+      <c r="V63" s="54" t="n"/>
+      <c r="W63" s="54" t="n"/>
+      <c r="X63" s="54" t="n"/>
+      <c r="Y63" s="54" t="n"/>
+      <c r="Z63" s="54" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B64" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z64" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
+        <is>
+          <t>25년말</t>
+        </is>
+      </c>
+      <c r="B65" s="60" t="n">
+        <v>161</v>
+      </c>
+      <c r="Z65" s="59" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="56" t="inlineStr">
-        <is>
-          <t>2Q</t>
-        </is>
-      </c>
-      <c r="B62" s="57" t="n">
-        <v>108.8</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="56" t="inlineStr">
-        <is>
-          <t>3Q</t>
-        </is>
-      </c>
-      <c r="B63" s="57" t="n">
-        <v>107.9</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="56" t="inlineStr">
-        <is>
-          <t>9M</t>
-        </is>
-      </c>
-      <c r="B64" s="57" t="n">
-        <v>107.8</v>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
+        <is>
+          <t>26년말 계획</t>
+        </is>
+      </c>
+      <c r="B66" s="60" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="54" t="inlineStr">
+        <is>
+          <t>this results · bs 3q</t>
+        </is>
+      </c>
+      <c r="B68" s="54" t="n"/>
+      <c r="C68" s="54" t="n"/>
+      <c r="D68" s="54" t="n"/>
+      <c r="E68" s="54" t="n"/>
+      <c r="F68" s="54" t="n"/>
+      <c r="G68" s="54" t="n"/>
+      <c r="H68" s="54" t="n"/>
+      <c r="I68" s="54" t="n"/>
+      <c r="J68" s="54" t="n"/>
+      <c r="K68" s="54" t="n"/>
+      <c r="L68" s="54" t="n"/>
+      <c r="M68" s="54" t="n"/>
+      <c r="N68" s="54" t="n"/>
+      <c r="O68" s="54" t="n"/>
+      <c r="P68" s="54" t="n"/>
+      <c r="Q68" s="54" t="n"/>
+      <c r="R68" s="54" t="n"/>
+      <c r="S68" s="54" t="n"/>
+      <c r="T68" s="54" t="n"/>
+      <c r="U68" s="54" t="n"/>
+      <c r="V68" s="54" t="n"/>
+      <c r="W68" s="54" t="n"/>
+      <c r="X68" s="54" t="n"/>
+      <c r="Y68" s="54" t="n"/>
+      <c r="Z68" s="54" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B69" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z69" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="56" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B70" s="57" t="n">
+        <v>104.57</v>
+      </c>
+      <c r="Z70" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="56" t="inlineStr">
+        <is>
+          <t>합계 assets</t>
+        </is>
+      </c>
+      <c r="B71" s="57" t="n">
+        <v>289.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="56" t="inlineStr">
+        <is>
+          <t>equity ratio</t>
+        </is>
+      </c>
+      <c r="B72" s="57" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="54" t="inlineStr">
+        <is>
+          <t>annual 실적 EPS post split</t>
+        </is>
+      </c>
+      <c r="B74" s="54" t="n"/>
+      <c r="C74" s="54" t="n"/>
+      <c r="D74" s="54" t="n"/>
+      <c r="E74" s="54" t="n"/>
+      <c r="F74" s="54" t="n"/>
+      <c r="G74" s="54" t="n"/>
+      <c r="H74" s="54" t="n"/>
+      <c r="I74" s="54" t="n"/>
+      <c r="J74" s="54" t="n"/>
+      <c r="K74" s="54" t="n"/>
+      <c r="L74" s="54" t="n"/>
+      <c r="M74" s="54" t="n"/>
+      <c r="N74" s="54" t="n"/>
+      <c r="O74" s="54" t="n"/>
+      <c r="P74" s="54" t="n"/>
+      <c r="Q74" s="54" t="n"/>
+      <c r="R74" s="54" t="n"/>
+      <c r="S74" s="54" t="n"/>
+      <c r="T74" s="54" t="n"/>
+      <c r="U74" s="54" t="n"/>
+      <c r="V74" s="54" t="n"/>
+      <c r="W74" s="54" t="n"/>
+      <c r="X74" s="54" t="n"/>
+      <c r="Y74" s="54" t="n"/>
+      <c r="Z74" s="54" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B75" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z75" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="56" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B76" s="57" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Z76" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="56" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B77" s="57" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="56" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B78" s="57" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B79" s="57" t="n">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="54" t="inlineStr">
+        <is>
+          <t>dps post split</t>
+        </is>
+      </c>
+      <c r="B81" s="54" t="n"/>
+      <c r="C81" s="54" t="n"/>
+      <c r="D81" s="54" t="n"/>
+      <c r="E81" s="54" t="n"/>
+      <c r="F81" s="54" t="n"/>
+      <c r="G81" s="54" t="n"/>
+      <c r="H81" s="54" t="n"/>
+      <c r="I81" s="54" t="n"/>
+      <c r="J81" s="54" t="n"/>
+      <c r="K81" s="54" t="n"/>
+      <c r="L81" s="54" t="n"/>
+      <c r="M81" s="54" t="n"/>
+      <c r="N81" s="54" t="n"/>
+      <c r="O81" s="54" t="n"/>
+      <c r="P81" s="54" t="n"/>
+      <c r="Q81" s="54" t="n"/>
+      <c r="R81" s="54" t="n"/>
+      <c r="S81" s="54" t="n"/>
+      <c r="T81" s="54" t="n"/>
+      <c r="U81" s="54" t="n"/>
+      <c r="V81" s="54" t="n"/>
+      <c r="W81" s="54" t="n"/>
+      <c r="X81" s="54" t="n"/>
+      <c r="Y81" s="54" t="n"/>
+      <c r="Z81" s="54" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B82" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z82" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="56" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B83" s="60" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z83" s="59" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="56" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B84" s="60" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B85" s="60" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="54" t="inlineStr">
+        <is>
+          <t>컨센서스</t>
+        </is>
+      </c>
+      <c r="B87" s="54" t="n"/>
+      <c r="C87" s="54" t="n"/>
+      <c r="D87" s="54" t="n"/>
+      <c r="E87" s="54" t="n"/>
+      <c r="F87" s="54" t="n"/>
+      <c r="G87" s="54" t="n"/>
+      <c r="H87" s="54" t="n"/>
+      <c r="I87" s="54" t="n"/>
+      <c r="J87" s="54" t="n"/>
+      <c r="K87" s="54" t="n"/>
+      <c r="L87" s="54" t="n"/>
+      <c r="M87" s="54" t="n"/>
+      <c r="N87" s="54" t="n"/>
+      <c r="O87" s="54" t="n"/>
+      <c r="P87" s="54" t="n"/>
+      <c r="Q87" s="54" t="n"/>
+      <c r="R87" s="54" t="n"/>
+      <c r="S87" s="54" t="n"/>
+      <c r="T87" s="54" t="n"/>
+      <c r="U87" s="54" t="n"/>
+      <c r="V87" s="54" t="n"/>
+      <c r="W87" s="54" t="n"/>
+      <c r="X87" s="54" t="n"/>
+      <c r="Y87" s="54" t="n"/>
+      <c r="Z87" s="54" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B88" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z88" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="56" t="inlineStr">
+        <is>
+          <t>4Q26 매출</t>
+        </is>
+      </c>
+      <c r="B89" s="57" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z89" s="59" t="inlineStr">
+        <is>
+          <t>야후 jp_consensus 2026-10-29 · 애널리스트 2명(컨센이라 부르지 말 것)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="56" t="inlineStr">
+        <is>
+          <t>trailing pe</t>
+        </is>
+      </c>
+      <c r="B90" s="57" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="54" t="inlineStr">
+        <is>
+          <t>컨센서스 · fy26</t>
+        </is>
+      </c>
+      <c r="B92" s="54" t="n"/>
+      <c r="C92" s="54" t="n"/>
+      <c r="D92" s="54" t="n"/>
+      <c r="E92" s="54" t="n"/>
+      <c r="F92" s="54" t="n"/>
+      <c r="G92" s="54" t="n"/>
+      <c r="H92" s="54" t="n"/>
+      <c r="I92" s="54" t="n"/>
+      <c r="J92" s="54" t="n"/>
+      <c r="K92" s="54" t="n"/>
+      <c r="L92" s="54" t="n"/>
+      <c r="M92" s="54" t="n"/>
+      <c r="N92" s="54" t="n"/>
+      <c r="O92" s="54" t="n"/>
+      <c r="P92" s="54" t="n"/>
+      <c r="Q92" s="54" t="n"/>
+      <c r="R92" s="54" t="n"/>
+      <c r="S92" s="54" t="n"/>
+      <c r="T92" s="54" t="n"/>
+      <c r="U92" s="54" t="n"/>
+      <c r="V92" s="54" t="n"/>
+      <c r="W92" s="54" t="n"/>
+      <c r="X92" s="54" t="n"/>
+      <c r="Y92" s="54" t="n"/>
+      <c r="Z92" s="54" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z93" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B94" s="57" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="Z94" s="59" t="inlineStr">
+        <is>
+          <t>야후 jp_consensus 2026-10-29 · 애널리스트 2명(컨센이라 부르지 말 것)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B95" s="57" t="n">
+        <v>90.95</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="54" t="inlineStr">
+        <is>
+          <t>컨센서스 · fy27</t>
+        </is>
+      </c>
+      <c r="B97" s="54" t="n"/>
+      <c r="C97" s="54" t="n"/>
+      <c r="D97" s="54" t="n"/>
+      <c r="E97" s="54" t="n"/>
+      <c r="F97" s="54" t="n"/>
+      <c r="G97" s="54" t="n"/>
+      <c r="H97" s="54" t="n"/>
+      <c r="I97" s="54" t="n"/>
+      <c r="J97" s="54" t="n"/>
+      <c r="K97" s="54" t="n"/>
+      <c r="L97" s="54" t="n"/>
+      <c r="M97" s="54" t="n"/>
+      <c r="N97" s="54" t="n"/>
+      <c r="O97" s="54" t="n"/>
+      <c r="P97" s="54" t="n"/>
+      <c r="Q97" s="54" t="n"/>
+      <c r="R97" s="54" t="n"/>
+      <c r="S97" s="54" t="n"/>
+      <c r="T97" s="54" t="n"/>
+      <c r="U97" s="54" t="n"/>
+      <c r="V97" s="54" t="n"/>
+      <c r="W97" s="54" t="n"/>
+      <c r="X97" s="54" t="n"/>
+      <c r="Y97" s="54" t="n"/>
+      <c r="Z97" s="54" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B98" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z98" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B99" s="57" t="n">
+        <v>372</v>
+      </c>
+      <c r="Z99" s="59" t="inlineStr">
+        <is>
+          <t>야후 jp_consensus 2026-10-29 · 애널리스트 2명(컨센이라 부르지 말 것)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B100" s="57" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="54" t="inlineStr">
+        <is>
+          <t>컨센서스 · 목표주가 가격</t>
+        </is>
+      </c>
+      <c r="B102" s="54" t="n"/>
+      <c r="C102" s="54" t="n"/>
+      <c r="D102" s="54" t="n"/>
+      <c r="E102" s="54" t="n"/>
+      <c r="F102" s="54" t="n"/>
+      <c r="G102" s="54" t="n"/>
+      <c r="H102" s="54" t="n"/>
+      <c r="I102" s="54" t="n"/>
+      <c r="J102" s="54" t="n"/>
+      <c r="K102" s="54" t="n"/>
+      <c r="L102" s="54" t="n"/>
+      <c r="M102" s="54" t="n"/>
+      <c r="N102" s="54" t="n"/>
+      <c r="O102" s="54" t="n"/>
+      <c r="P102" s="54" t="n"/>
+      <c r="Q102" s="54" t="n"/>
+      <c r="R102" s="54" t="n"/>
+      <c r="S102" s="54" t="n"/>
+      <c r="T102" s="54" t="n"/>
+      <c r="U102" s="54" t="n"/>
+      <c r="V102" s="54" t="n"/>
+      <c r="W102" s="54" t="n"/>
+      <c r="X102" s="54" t="n"/>
+      <c r="Y102" s="54" t="n"/>
+      <c r="Z102" s="54" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B103" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="Z103" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="56" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="B104" s="60" t="n">
+        <v>2800</v>
+      </c>
+      <c r="Z104" s="59" t="inlineStr">
+        <is>
+          <t>야후 jp_consensus 2026-10-29 · 애널리스트 2명(컨센이라 부르지 말 것)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="56" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B105" s="60" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17943,17 +19024,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
